--- a/PEWI Budgets 2024$ - 2025$ (021425).xlsx
+++ b/PEWI Budgets 2024$ - 2025$ (021425).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_pewi\pewi3.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_pewi\PEWI-People-in-Ecosystem-and-Watershed-Integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8295792B-1A7B-437F-90D3-F70EBA989AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882B919A-B065-496D-8BE9-D3E793EF560B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3870" yWindow="660" windowWidth="21600" windowHeight="13185" activeTab="7" xr2:uid="{2A59C1DF-064D-264D-B5F5-440AD859B569}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2A59C1DF-064D-264D-B5F5-440AD859B569}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions &amp; summary data" sheetId="19" r:id="rId1"/>
@@ -33,6 +33,9 @@
     <sheet name="Fruits &amp; Veg" sheetId="18" r:id="rId18"/>
     <sheet name="SRWC (discard " sheetId="15" r:id="rId19"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Instructions &amp; summary data'!$B$32:$E$32</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -52,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="579">
   <si>
     <t>Ag Decision Maker -- Iowa State University Extension and Outreach</t>
   </si>
@@ -2136,6 +2139,54 @@
   <si>
     <t>500 Acres</t>
   </si>
+  <si>
+    <t>Land use</t>
+  </si>
+  <si>
+    <t>Unit price</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Conventional Soybean</t>
+  </si>
+  <si>
+    <t>Switchgrass Bioenergy</t>
+  </si>
+  <si>
+    <t>Short-Rotation Woody Biomass</t>
+  </si>
+  <si>
+    <t>Soybean following Corn</t>
+  </si>
+  <si>
+    <t>Corn following Soybean</t>
+  </si>
+  <si>
+    <t>Corn following Corn</t>
+  </si>
+  <si>
+    <t>Carbon Credit</t>
+  </si>
+  <si>
+    <t>Nitrate Credits</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mg </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>−1</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -2152,7 +2203,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="55">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2504,6 +2555,25 @@
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="19">
@@ -3216,7 +3286,7 @@
     <xf numFmtId="7" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="520">
+  <cellXfs count="521">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -4288,6 +4358,7 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="51" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4336,42 +4407,42 @@
     <xf numFmtId="44" fontId="0" fillId="12" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="8" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4384,7 +4455,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -5232,7 +5305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE1E20D6-F156-C447-BE27-5EDB562A8E09}">
-  <dimension ref="B2:M30"/>
+  <dimension ref="B2:M51"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -5265,20 +5338,20 @@
       <c r="E4" s="454" t="s">
         <v>485</v>
       </c>
-      <c r="F4" s="487" t="s">
+      <c r="F4" s="488" t="s">
         <v>480</v>
       </c>
-      <c r="G4" s="487"/>
+      <c r="G4" s="488"/>
       <c r="H4" s="454" t="s">
         <v>545</v>
       </c>
-      <c r="I4" s="488" t="s">
+      <c r="I4" s="489" t="s">
         <v>77</v>
       </c>
-      <c r="J4" s="488"/>
-      <c r="K4" s="488"/>
-      <c r="L4" s="488"/>
-      <c r="M4" s="488"/>
+      <c r="J4" s="489"/>
+      <c r="K4" s="489"/>
+      <c r="L4" s="489"/>
+      <c r="M4" s="489"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" t="s">
@@ -5729,11 +5802,197 @@
         <v>512</v>
       </c>
     </row>
+    <row r="32" spans="2:9">
+      <c r="B32" t="s">
+        <v>567</v>
+      </c>
+      <c r="C32" t="s">
+        <v>568</v>
+      </c>
+      <c r="D32" t="s">
+        <v>183</v>
+      </c>
+      <c r="E32" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="16.5" thickBot="1">
+      <c r="B33" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" ht="16.5" thickBot="1">
+      <c r="B34" t="s">
+        <v>575</v>
+      </c>
+      <c r="C34">
+        <v>171.23</v>
+      </c>
+      <c r="D34" s="520" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" t="s">
+        <v>574</v>
+      </c>
+      <c r="C35">
+        <v>171.23</v>
+      </c>
+      <c r="D35" s="520" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="16.5" thickBot="1">
+      <c r="B36" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="16.5" thickBot="1">
+      <c r="B37" t="s">
+        <v>573</v>
+      </c>
+      <c r="C37">
+        <v>381.07</v>
+      </c>
+      <c r="D37" s="520" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="16.5" thickBot="1">
+      <c r="B38" t="s">
+        <v>456</v>
+      </c>
+      <c r="C38">
+        <v>171.23</v>
+      </c>
+      <c r="D38" s="520" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="16.5" thickBot="1">
+      <c r="B39" t="s">
+        <v>458</v>
+      </c>
+      <c r="C39">
+        <v>481.29</v>
+      </c>
+      <c r="D39" s="520" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" ht="16.5" thickBot="1">
+      <c r="B40" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40">
+        <v>253</v>
+      </c>
+      <c r="D40" s="520" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" ht="16.5" thickBot="1">
+      <c r="B41" t="s">
+        <v>473</v>
+      </c>
+      <c r="C41">
+        <v>180</v>
+      </c>
+      <c r="D41" s="520" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" ht="16.5" thickBot="1">
+      <c r="B42" t="s">
+        <v>571</v>
+      </c>
+      <c r="C42">
+        <v>60</v>
+      </c>
+      <c r="D42" s="520" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" t="s">
+        <v>572</v>
+      </c>
+      <c r="C43">
+        <v>60</v>
+      </c>
+      <c r="D43" s="520" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" t="s">
+        <v>463</v>
+      </c>
+      <c r="C44">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" t="s">
+        <v>464</v>
+      </c>
+      <c r="C45">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" t="s">
+        <v>469</v>
+      </c>
+      <c r="C46">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" t="s">
+        <v>470</v>
+      </c>
+      <c r="C47">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" t="s">
+        <v>576</v>
+      </c>
+      <c r="C48">
+        <v>40.82</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3">
+      <c r="B49" t="s">
+        <v>467</v>
+      </c>
+      <c r="C49">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3">
+      <c r="B50" t="s">
+        <v>468</v>
+      </c>
+      <c r="C50">
+        <v>312.08999999999997</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3">
+      <c r="B51" t="s">
+        <v>577</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="B32:E32" xr:uid="{AE1E20D6-F156-C447-BE27-5EDB562A8E09}"/>
   <mergeCells count="2">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="I4:M4"/>
   </mergeCells>
+  <phoneticPr fontId="54" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B6" location="'C following C'!A1" display="      C following C" xr:uid="{AB38E860-2C4B-514B-A422-B13CC6C895CD}"/>
     <hyperlink ref="B7" location="'C following SB'!A1" display="      C following SB" xr:uid="{B12C751E-B78B-EC41-A366-BA3D72AD89A7}"/>
@@ -5753,6 +6012,7 @@
     <hyperlink ref="B22" location="'Wetland Restoration'!A1" display="Wetland restoration" xr:uid="{96697A32-403B-6742-A852-24D9D4D99E2C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6289,14 +6549,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24">
-      <c r="M2" s="491" t="s">
+      <c r="M2" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="N2" s="491"/>
+      <c r="N2" s="492"/>
     </row>
     <row r="3" spans="1:24" ht="16.5" thickBot="1">
-      <c r="M3" s="492"/>
-      <c r="N3" s="492"/>
+      <c r="M3" s="493"/>
+      <c r="N3" s="493"/>
     </row>
     <row r="4" spans="1:24" ht="16.5" thickBot="1">
       <c r="A4" s="347" t="s">
@@ -8087,71 +8347,71 @@
       </c>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="500" t="s">
+      <c r="A57" s="501" t="s">
         <v>551</v>
       </c>
-      <c r="B57" s="500"/>
-      <c r="C57" s="500"/>
-      <c r="D57" s="500"/>
-      <c r="E57" s="500"/>
-      <c r="F57" s="500"/>
-      <c r="G57" s="500"/>
-      <c r="H57" s="500"/>
-      <c r="I57" s="500"/>
-      <c r="J57" s="500"/>
-      <c r="K57" s="500"/>
+      <c r="B57" s="501"/>
+      <c r="C57" s="501"/>
+      <c r="D57" s="501"/>
+      <c r="E57" s="501"/>
+      <c r="F57" s="501"/>
+      <c r="G57" s="501"/>
+      <c r="H57" s="501"/>
+      <c r="I57" s="501"/>
+      <c r="J57" s="501"/>
+      <c r="K57" s="501"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="500"/>
-      <c r="B58" s="500"/>
-      <c r="C58" s="500"/>
-      <c r="D58" s="500"/>
-      <c r="E58" s="500"/>
-      <c r="F58" s="500"/>
-      <c r="G58" s="500"/>
-      <c r="H58" s="500"/>
-      <c r="I58" s="500"/>
-      <c r="J58" s="500"/>
-      <c r="K58" s="500"/>
+      <c r="A58" s="501"/>
+      <c r="B58" s="501"/>
+      <c r="C58" s="501"/>
+      <c r="D58" s="501"/>
+      <c r="E58" s="501"/>
+      <c r="F58" s="501"/>
+      <c r="G58" s="501"/>
+      <c r="H58" s="501"/>
+      <c r="I58" s="501"/>
+      <c r="J58" s="501"/>
+      <c r="K58" s="501"/>
     </row>
     <row r="59" spans="1:12" ht="6.95" customHeight="1">
-      <c r="A59" s="500"/>
-      <c r="B59" s="500"/>
-      <c r="C59" s="500"/>
-      <c r="D59" s="500"/>
-      <c r="E59" s="500"/>
-      <c r="F59" s="500"/>
-      <c r="G59" s="500"/>
-      <c r="H59" s="500"/>
-      <c r="I59" s="500"/>
-      <c r="J59" s="500"/>
-      <c r="K59" s="500"/>
+      <c r="A59" s="501"/>
+      <c r="B59" s="501"/>
+      <c r="C59" s="501"/>
+      <c r="D59" s="501"/>
+      <c r="E59" s="501"/>
+      <c r="F59" s="501"/>
+      <c r="G59" s="501"/>
+      <c r="H59" s="501"/>
+      <c r="I59" s="501"/>
+      <c r="J59" s="501"/>
+      <c r="K59" s="501"/>
     </row>
     <row r="60" spans="1:12" ht="8.1" customHeight="1">
-      <c r="A60" s="500"/>
-      <c r="B60" s="500"/>
-      <c r="C60" s="500"/>
-      <c r="D60" s="500"/>
-      <c r="E60" s="500"/>
-      <c r="F60" s="500"/>
-      <c r="G60" s="500"/>
-      <c r="H60" s="500"/>
-      <c r="I60" s="500"/>
-      <c r="J60" s="500"/>
-      <c r="K60" s="500"/>
+      <c r="A60" s="501"/>
+      <c r="B60" s="501"/>
+      <c r="C60" s="501"/>
+      <c r="D60" s="501"/>
+      <c r="E60" s="501"/>
+      <c r="F60" s="501"/>
+      <c r="G60" s="501"/>
+      <c r="H60" s="501"/>
+      <c r="I60" s="501"/>
+      <c r="J60" s="501"/>
+      <c r="K60" s="501"/>
     </row>
     <row r="61" spans="1:12" ht="6.95" customHeight="1">
-      <c r="A61" s="500"/>
-      <c r="B61" s="500"/>
-      <c r="C61" s="500"/>
-      <c r="D61" s="500"/>
-      <c r="E61" s="500"/>
-      <c r="F61" s="500"/>
-      <c r="G61" s="500"/>
-      <c r="H61" s="500"/>
-      <c r="I61" s="500"/>
-      <c r="J61" s="500"/>
-      <c r="K61" s="500"/>
+      <c r="A61" s="501"/>
+      <c r="B61" s="501"/>
+      <c r="C61" s="501"/>
+      <c r="D61" s="501"/>
+      <c r="E61" s="501"/>
+      <c r="F61" s="501"/>
+      <c r="G61" s="501"/>
+      <c r="H61" s="501"/>
+      <c r="I61" s="501"/>
+      <c r="J61" s="501"/>
+      <c r="K61" s="501"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8177,29 +8437,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12">
-      <c r="K2" s="491" t="s">
+      <c r="K2" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="L2" s="491"/>
+      <c r="L2" s="492"/>
     </row>
     <row r="3" spans="2:12" ht="21.75" thickBot="1">
       <c r="B3" s="144" t="s">
         <v>416</v>
       </c>
-      <c r="K3" s="492"/>
-      <c r="L3" s="492"/>
+      <c r="K3" s="493"/>
+      <c r="L3" s="493"/>
     </row>
     <row r="4" spans="2:12" ht="33.75">
-      <c r="B4" s="506" t="s">
+      <c r="B4" s="504" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="507"/>
-      <c r="D4" s="507"/>
-      <c r="E4" s="507"/>
-      <c r="F4" s="507"/>
-      <c r="G4" s="507"/>
-      <c r="H4" s="507"/>
-      <c r="I4" s="508"/>
+      <c r="C4" s="505"/>
+      <c r="D4" s="505"/>
+      <c r="E4" s="505"/>
+      <c r="F4" s="505"/>
+      <c r="G4" s="505"/>
+      <c r="H4" s="505"/>
+      <c r="I4" s="506"/>
     </row>
     <row r="5" spans="2:12" ht="16.5" thickBot="1">
       <c r="B5" s="145" t="s">
@@ -8220,10 +8480,10 @@
       <c r="G5" s="146" t="s">
         <v>200</v>
       </c>
-      <c r="H5" s="509" t="s">
+      <c r="H5" s="507" t="s">
         <v>201</v>
       </c>
-      <c r="I5" s="510"/>
+      <c r="I5" s="508"/>
     </row>
     <row r="6" spans="2:12" ht="16.5" thickBot="1">
       <c r="B6" s="147"/>
@@ -8301,10 +8561,10 @@
       <c r="G9" s="150" t="s">
         <v>200</v>
       </c>
-      <c r="H9" s="511" t="s">
+      <c r="H9" s="509" t="s">
         <v>212</v>
       </c>
-      <c r="I9" s="512"/>
+      <c r="I9" s="510"/>
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="151" t="s">
@@ -8328,11 +8588,11 @@
         <f>F10/C6</f>
         <v>160</v>
       </c>
-      <c r="H10" s="503">
+      <c r="H10" s="511">
         <f>G10/$I$7</f>
         <v>290.90909090909088</v>
       </c>
-      <c r="I10" s="504"/>
+      <c r="I10" s="512"/>
     </row>
     <row r="11" spans="2:12" ht="17.25">
       <c r="B11" s="157" t="s">
@@ -8427,11 +8687,11 @@
         <f>F15/20</f>
         <v>25</v>
       </c>
-      <c r="H15" s="501">
+      <c r="H15" s="502">
         <f>G15/$I$8</f>
         <v>3.787878787878788E-2</v>
       </c>
-      <c r="I15" s="502"/>
+      <c r="I15" s="503"/>
     </row>
     <row r="16" spans="2:12">
       <c r="B16" s="147" t="s">
@@ -8455,11 +8715,11 @@
         <f>F16/20</f>
         <v>15</v>
       </c>
-      <c r="H16" s="501">
+      <c r="H16" s="502">
         <f t="shared" ref="H16:H31" si="0">G16/$I$8</f>
         <v>2.2727272727272728E-2</v>
       </c>
-      <c r="I16" s="502"/>
+      <c r="I16" s="503"/>
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="147" t="s">
@@ -8483,11 +8743,11 @@
         <f>F17/20</f>
         <v>27.5</v>
       </c>
-      <c r="H17" s="501">
+      <c r="H17" s="502">
         <f t="shared" si="0"/>
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="I17" s="502"/>
+      <c r="I17" s="503"/>
     </row>
     <row r="18" spans="2:10">
       <c r="B18" s="147" t="s">
@@ -8511,11 +8771,11 @@
       <c r="G18" s="422">
         <v>1.25</v>
       </c>
-      <c r="H18" s="501">
+      <c r="H18" s="502">
         <f t="shared" si="0"/>
         <v>1.893939393939394E-3</v>
       </c>
-      <c r="I18" s="502"/>
+      <c r="I18" s="503"/>
     </row>
     <row r="19" spans="2:10">
       <c r="B19" s="147" t="s">
@@ -8538,11 +8798,11 @@
       <c r="G19" s="422">
         <v>1</v>
       </c>
-      <c r="H19" s="501">
+      <c r="H19" s="502">
         <f t="shared" si="0"/>
         <v>1.5151515151515152E-3</v>
       </c>
-      <c r="I19" s="502"/>
+      <c r="I19" s="503"/>
     </row>
     <row r="20" spans="2:10">
       <c r="B20" s="147" t="s">
@@ -8566,11 +8826,11 @@
         <f>F20/20</f>
         <v>100</v>
       </c>
-      <c r="H20" s="501">
+      <c r="H20" s="502">
         <f t="shared" si="0"/>
         <v>0.15151515151515152</v>
       </c>
-      <c r="I20" s="502"/>
+      <c r="I20" s="503"/>
     </row>
     <row r="21" spans="2:10">
       <c r="B21" s="147" t="s">
@@ -8594,11 +8854,11 @@
         <f>F21/20</f>
         <v>1452.0000000000002</v>
       </c>
-      <c r="H21" s="501">
+      <c r="H21" s="502">
         <f t="shared" si="0"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="I21" s="502"/>
+      <c r="I21" s="503"/>
     </row>
     <row r="22" spans="2:10">
       <c r="B22" s="147" t="s">
@@ -8622,11 +8882,11 @@
         <f>F22/20</f>
         <v>35</v>
       </c>
-      <c r="H22" s="501">
+      <c r="H22" s="502">
         <f t="shared" si="0"/>
         <v>5.3030303030303032E-2</v>
       </c>
-      <c r="I22" s="502"/>
+      <c r="I22" s="503"/>
     </row>
     <row r="23" spans="2:10">
       <c r="B23" s="147" t="s">
@@ -8649,11 +8909,11 @@
       <c r="G23" s="422">
         <v>24</v>
       </c>
-      <c r="H23" s="501">
+      <c r="H23" s="502">
         <f t="shared" si="0"/>
         <v>3.6363636363636362E-2</v>
       </c>
-      <c r="I23" s="502"/>
+      <c r="I23" s="503"/>
     </row>
     <row r="24" spans="2:10">
       <c r="B24" s="147" t="s">
@@ -8676,11 +8936,11 @@
       <c r="G24" s="422">
         <v>185.40983606557376</v>
       </c>
-      <c r="H24" s="501">
+      <c r="H24" s="502">
         <f t="shared" si="0"/>
         <v>0.28092399403874813</v>
       </c>
-      <c r="I24" s="502"/>
+      <c r="I24" s="503"/>
     </row>
     <row r="25" spans="2:10">
       <c r="B25" s="147" t="s">
@@ -8703,11 +8963,11 @@
       <c r="G25" s="422">
         <v>13.65</v>
       </c>
-      <c r="H25" s="501">
+      <c r="H25" s="502">
         <f t="shared" si="0"/>
         <v>2.0681818181818183E-2</v>
       </c>
-      <c r="I25" s="502"/>
+      <c r="I25" s="503"/>
     </row>
     <row r="26" spans="2:10">
       <c r="B26" s="170" t="s">
@@ -8724,11 +8984,11 @@
         <f>SUM(G10:G25)</f>
         <v>2039.809836065574</v>
       </c>
-      <c r="H26" s="501">
+      <c r="H26" s="502">
         <f t="shared" si="0"/>
         <v>3.0906209637357183</v>
       </c>
-      <c r="I26" s="502"/>
+      <c r="I26" s="503"/>
     </row>
     <row r="27" spans="2:10">
       <c r="B27" s="172" t="s">
@@ -8736,11 +8996,11 @@
       </c>
       <c r="F27" s="422"/>
       <c r="G27" s="426"/>
-      <c r="H27" s="501">
+      <c r="H27" s="502">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="502"/>
+      <c r="I27" s="503"/>
     </row>
     <row r="28" spans="2:10">
       <c r="B28" s="147" t="s">
@@ -8753,11 +9013,11 @@
         <f>F28/20</f>
         <v>60</v>
       </c>
-      <c r="H28" s="501">
+      <c r="H28" s="502">
         <f t="shared" si="0"/>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="I28" s="502"/>
+      <c r="I28" s="503"/>
     </row>
     <row r="29" spans="2:10">
       <c r="B29" s="147" t="s">
@@ -8770,11 +9030,11 @@
         <f>F29/20</f>
         <v>22</v>
       </c>
-      <c r="H29" s="501">
+      <c r="H29" s="502">
         <f t="shared" si="0"/>
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="I29" s="502"/>
+      <c r="I29" s="503"/>
     </row>
     <row r="30" spans="2:10">
       <c r="B30" s="172" t="s">
@@ -8788,11 +9048,11 @@
         <f>G28+G29</f>
         <v>82</v>
       </c>
-      <c r="H30" s="501">
+      <c r="H30" s="502">
         <f t="shared" si="0"/>
         <v>0.12424242424242424</v>
       </c>
-      <c r="I30" s="502"/>
+      <c r="I30" s="503"/>
     </row>
     <row r="31" spans="2:10" ht="16.5" thickBot="1">
       <c r="B31" s="432" t="s">
@@ -8809,11 +9069,11 @@
         <f>G26+G6+G30</f>
         <v>3496.809836065574</v>
       </c>
-      <c r="H31" s="503">
+      <c r="H31" s="511">
         <f t="shared" si="0"/>
         <v>5.2981967213114753</v>
       </c>
-      <c r="I31" s="504"/>
+      <c r="I31" s="512"/>
       <c r="J31" t="s">
         <v>242</v>
       </c>
@@ -8855,11 +9115,11 @@
       <c r="I33" s="168"/>
     </row>
     <row r="34" spans="1:12" ht="17.25">
-      <c r="B34" s="505" t="s">
+      <c r="B34" s="515" t="s">
         <v>245</v>
       </c>
-      <c r="C34" s="505"/>
-      <c r="D34" s="505"/>
+      <c r="C34" s="515"/>
+      <c r="D34" s="515"/>
       <c r="L34">
         <f>50/H38</f>
         <v>2.1917808219178081</v>
@@ -8896,13 +9156,11 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="K2:L3"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="H27:I27"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="H17:I17"/>
@@ -8915,11 +9173,13 @@
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="H25:I25"/>
     <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="K2:L3"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L8" r:id="rId1" xr:uid="{F7409163-740C-D24A-84CB-4E3439D40069}"/>
@@ -8942,29 +9202,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12">
-      <c r="K2" s="491" t="s">
+      <c r="K2" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="L2" s="491"/>
+      <c r="L2" s="492"/>
     </row>
     <row r="3" spans="2:12" ht="21.75" thickBot="1">
       <c r="B3" s="144" t="s">
         <v>247</v>
       </c>
-      <c r="K3" s="492"/>
-      <c r="L3" s="492"/>
+      <c r="K3" s="493"/>
+      <c r="L3" s="493"/>
     </row>
     <row r="4" spans="2:12" ht="33.75">
-      <c r="B4" s="506" t="s">
+      <c r="B4" s="504" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="507"/>
-      <c r="D4" s="507"/>
-      <c r="E4" s="507"/>
-      <c r="F4" s="507"/>
-      <c r="G4" s="507"/>
-      <c r="H4" s="507"/>
-      <c r="I4" s="508"/>
+      <c r="C4" s="505"/>
+      <c r="D4" s="505"/>
+      <c r="E4" s="505"/>
+      <c r="F4" s="505"/>
+      <c r="G4" s="505"/>
+      <c r="H4" s="505"/>
+      <c r="I4" s="506"/>
     </row>
     <row r="5" spans="2:12" ht="16.5" thickBot="1">
       <c r="B5" s="145" t="s">
@@ -8985,10 +9245,10 @@
       <c r="G5" s="146" t="s">
         <v>200</v>
       </c>
-      <c r="H5" s="509" t="s">
+      <c r="H5" s="507" t="s">
         <v>201</v>
       </c>
-      <c r="I5" s="510"/>
+      <c r="I5" s="508"/>
     </row>
     <row r="6" spans="2:12" ht="16.5" thickBot="1">
       <c r="B6" s="147"/>
@@ -9066,10 +9326,10 @@
       <c r="G9" s="150" t="s">
         <v>200</v>
       </c>
-      <c r="H9" s="511" t="s">
+      <c r="H9" s="509" t="s">
         <v>212</v>
       </c>
-      <c r="I9" s="512"/>
+      <c r="I9" s="510"/>
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="151" t="s">
@@ -9093,11 +9353,11 @@
         <f>F10/C6</f>
         <v>160</v>
       </c>
-      <c r="H10" s="503" t="e">
+      <c r="H10" s="511" t="e">
         <f>G10/$J$7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I10" s="504"/>
+      <c r="I10" s="512"/>
     </row>
     <row r="11" spans="2:12" ht="17.25">
       <c r="B11" s="157" t="s">
@@ -9192,11 +9452,11 @@
         <f>F15/C6</f>
         <v>25</v>
       </c>
-      <c r="H15" s="501">
+      <c r="H15" s="502">
         <f>G15/$I$8</f>
         <v>3.787878787878788E-2</v>
       </c>
-      <c r="I15" s="502"/>
+      <c r="I15" s="503"/>
     </row>
     <row r="16" spans="2:12">
       <c r="B16" s="147" t="s">
@@ -9220,11 +9480,11 @@
         <f>F16/C6</f>
         <v>15</v>
       </c>
-      <c r="H16" s="501">
+      <c r="H16" s="502">
         <f t="shared" ref="H16:H32" si="1">G16/$I$8</f>
         <v>2.2727272727272728E-2</v>
       </c>
-      <c r="I16" s="502"/>
+      <c r="I16" s="503"/>
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="147" t="s">
@@ -9248,11 +9508,11 @@
         <f>F17/C6</f>
         <v>27.5</v>
       </c>
-      <c r="H17" s="501">
+      <c r="H17" s="502">
         <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="I17" s="502"/>
+      <c r="I17" s="503"/>
     </row>
     <row r="18" spans="2:10">
       <c r="B18" s="147" t="s">
@@ -9276,11 +9536,11 @@
       <c r="G18" s="422">
         <v>1.25</v>
       </c>
-      <c r="H18" s="501">
+      <c r="H18" s="502">
         <f t="shared" si="1"/>
         <v>1.893939393939394E-3</v>
       </c>
-      <c r="I18" s="502"/>
+      <c r="I18" s="503"/>
     </row>
     <row r="19" spans="2:10">
       <c r="B19" s="147" t="s">
@@ -9304,11 +9564,11 @@
         <f>D19</f>
         <v>60</v>
       </c>
-      <c r="H19" s="501">
+      <c r="H19" s="502">
         <f t="shared" ref="H19" si="2">G19/$I$8</f>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="I19" s="502"/>
+      <c r="I19" s="503"/>
     </row>
     <row r="20" spans="2:10">
       <c r="B20" s="147"/>
@@ -9329,11 +9589,11 @@
       <c r="G20" s="422">
         <v>1</v>
       </c>
-      <c r="H20" s="501">
+      <c r="H20" s="502">
         <f t="shared" si="1"/>
         <v>1.5151515151515152E-3</v>
       </c>
-      <c r="I20" s="502"/>
+      <c r="I20" s="503"/>
     </row>
     <row r="21" spans="2:10">
       <c r="B21" s="147" t="s">
@@ -9357,11 +9617,11 @@
         <f>F21/20</f>
         <v>100</v>
       </c>
-      <c r="H21" s="501">
+      <c r="H21" s="502">
         <f t="shared" si="1"/>
         <v>0.15151515151515152</v>
       </c>
-      <c r="I21" s="502"/>
+      <c r="I21" s="503"/>
     </row>
     <row r="22" spans="2:10">
       <c r="B22" s="147" t="s">
@@ -9385,11 +9645,11 @@
         <f>F22/20</f>
         <v>1452.0000000000002</v>
       </c>
-      <c r="H22" s="501">
+      <c r="H22" s="502">
         <f t="shared" si="1"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="I22" s="502"/>
+      <c r="I22" s="503"/>
     </row>
     <row r="23" spans="2:10">
       <c r="B23" s="147" t="s">
@@ -9413,11 +9673,11 @@
         <f>F23/20</f>
         <v>35</v>
       </c>
-      <c r="H23" s="501">
+      <c r="H23" s="502">
         <f t="shared" si="1"/>
         <v>5.3030303030303032E-2</v>
       </c>
-      <c r="I23" s="502"/>
+      <c r="I23" s="503"/>
     </row>
     <row r="24" spans="2:10">
       <c r="B24" s="147" t="s">
@@ -9440,11 +9700,11 @@
       <c r="G24" s="422">
         <v>24</v>
       </c>
-      <c r="H24" s="501">
+      <c r="H24" s="502">
         <f t="shared" si="1"/>
         <v>3.6363636363636362E-2</v>
       </c>
-      <c r="I24" s="502"/>
+      <c r="I24" s="503"/>
     </row>
     <row r="25" spans="2:10">
       <c r="B25" s="147" t="s">
@@ -9467,11 +9727,11 @@
       <c r="G25" s="422">
         <v>185.40983606557376</v>
       </c>
-      <c r="H25" s="501">
+      <c r="H25" s="502">
         <f t="shared" si="1"/>
         <v>0.28092399403874813</v>
       </c>
-      <c r="I25" s="502"/>
+      <c r="I25" s="503"/>
     </row>
     <row r="26" spans="2:10">
       <c r="B26" s="147" t="s">
@@ -9494,11 +9754,11 @@
       <c r="G26" s="422">
         <v>13.65</v>
       </c>
-      <c r="H26" s="501">
+      <c r="H26" s="502">
         <f t="shared" si="1"/>
         <v>2.0681818181818183E-2</v>
       </c>
-      <c r="I26" s="502"/>
+      <c r="I26" s="503"/>
     </row>
     <row r="27" spans="2:10">
       <c r="B27" s="170" t="s">
@@ -9515,11 +9775,11 @@
         <f>SUM(G10:G26)</f>
         <v>2099.809836065574</v>
       </c>
-      <c r="H27" s="501">
+      <c r="H27" s="502">
         <f t="shared" si="1"/>
         <v>3.1815300546448091</v>
       </c>
-      <c r="I27" s="502"/>
+      <c r="I27" s="503"/>
     </row>
     <row r="28" spans="2:10">
       <c r="B28" s="172" t="s">
@@ -9527,11 +9787,11 @@
       </c>
       <c r="F28" s="422"/>
       <c r="G28" s="426"/>
-      <c r="H28" s="501">
+      <c r="H28" s="502">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="502"/>
+      <c r="I28" s="503"/>
     </row>
     <row r="29" spans="2:10">
       <c r="B29" s="147" t="s">
@@ -9544,11 +9804,11 @@
         <f>F29/20</f>
         <v>60</v>
       </c>
-      <c r="H29" s="501">
+      <c r="H29" s="502">
         <f t="shared" si="1"/>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="I29" s="502"/>
+      <c r="I29" s="503"/>
     </row>
     <row r="30" spans="2:10">
       <c r="B30" s="147" t="s">
@@ -9561,11 +9821,11 @@
         <f>F30/20</f>
         <v>22</v>
       </c>
-      <c r="H30" s="501">
+      <c r="H30" s="502">
         <f t="shared" si="1"/>
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="I30" s="502"/>
+      <c r="I30" s="503"/>
     </row>
     <row r="31" spans="2:10">
       <c r="B31" s="172" t="s">
@@ -9579,11 +9839,11 @@
         <f>G29+G30</f>
         <v>82</v>
       </c>
-      <c r="H31" s="501">
+      <c r="H31" s="502">
         <f t="shared" si="1"/>
         <v>0.12424242424242424</v>
       </c>
-      <c r="I31" s="502"/>
+      <c r="I31" s="503"/>
     </row>
     <row r="32" spans="2:10" ht="16.5" thickBot="1">
       <c r="B32" s="432" t="s">
@@ -9600,11 +9860,11 @@
         <f>G27+G6+G31</f>
         <v>3556.809836065574</v>
       </c>
-      <c r="H32" s="503">
+      <c r="H32" s="511">
         <f t="shared" si="1"/>
         <v>5.3891058122205671</v>
       </c>
-      <c r="I32" s="504"/>
+      <c r="I32" s="512"/>
       <c r="J32" t="s">
         <v>242</v>
       </c>
@@ -9646,11 +9906,11 @@
       <c r="I34" s="168"/>
     </row>
     <row r="35" spans="1:9" ht="17.25">
-      <c r="B35" s="505" t="s">
+      <c r="B35" s="515" t="s">
         <v>245</v>
       </c>
-      <c r="C35" s="505"/>
-      <c r="D35" s="505"/>
+      <c r="C35" s="515"/>
+      <c r="D35" s="515"/>
     </row>
     <row r="36" spans="1:9" ht="17.25">
       <c r="B36" s="174" t="s">
@@ -9671,6 +9931,16 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
     <mergeCell ref="K2:L3"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="H28:I28"/>
@@ -9686,16 +9956,6 @@
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L8" r:id="rId1" xr:uid="{C10CBC37-B907-284D-A5CD-D379AFEFC3CE}"/>
@@ -9715,17 +9975,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="16.5" thickBot="1">
-      <c r="O2" s="491" t="s">
+      <c r="O2" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="P2" s="491"/>
+      <c r="P2" s="492"/>
     </row>
     <row r="3" spans="1:16" ht="16.5" thickBot="1">
       <c r="C3" s="178" t="s">
         <v>253</v>
       </c>
-      <c r="O3" s="492"/>
-      <c r="P3" s="492"/>
+      <c r="O3" s="493"/>
+      <c r="P3" s="493"/>
     </row>
     <row r="4" spans="1:16" ht="24" thickBot="1">
       <c r="B4" s="179" t="s">
@@ -9744,10 +10004,10 @@
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="C6" s="516" t="s">
+      <c r="C6" s="517" t="s">
         <v>256</v>
       </c>
-      <c r="D6" s="516"/>
+      <c r="D6" s="517"/>
       <c r="H6" t="s">
         <v>257</v>
       </c>
@@ -10316,36 +10576,36 @@
       </c>
     </row>
     <row r="31" spans="1:15">
-      <c r="C31" s="515" t="s">
+      <c r="C31" s="516" t="s">
         <v>293</v>
       </c>
-      <c r="D31" s="515"/>
-      <c r="E31" s="515"/>
-      <c r="F31" s="515"/>
-      <c r="G31" s="515"/>
-      <c r="H31" s="515"/>
-      <c r="I31" s="515"/>
-      <c r="J31" s="515"/>
-      <c r="K31" s="515"/>
-      <c r="L31" s="515"/>
-      <c r="M31" s="515"/>
-      <c r="N31" s="515"/>
-      <c r="O31" s="515"/>
+      <c r="D31" s="516"/>
+      <c r="E31" s="516"/>
+      <c r="F31" s="516"/>
+      <c r="G31" s="516"/>
+      <c r="H31" s="516"/>
+      <c r="I31" s="516"/>
+      <c r="J31" s="516"/>
+      <c r="K31" s="516"/>
+      <c r="L31" s="516"/>
+      <c r="M31" s="516"/>
+      <c r="N31" s="516"/>
+      <c r="O31" s="516"/>
     </row>
     <row r="32" spans="1:15">
-      <c r="C32" s="515"/>
-      <c r="D32" s="515"/>
-      <c r="E32" s="515"/>
-      <c r="F32" s="515"/>
-      <c r="G32" s="515"/>
-      <c r="H32" s="515"/>
-      <c r="I32" s="515"/>
-      <c r="J32" s="515"/>
-      <c r="K32" s="515"/>
-      <c r="L32" s="515"/>
-      <c r="M32" s="515"/>
-      <c r="N32" s="515"/>
-      <c r="O32" s="515"/>
+      <c r="C32" s="516"/>
+      <c r="D32" s="516"/>
+      <c r="E32" s="516"/>
+      <c r="F32" s="516"/>
+      <c r="G32" s="516"/>
+      <c r="H32" s="516"/>
+      <c r="I32" s="516"/>
+      <c r="J32" s="516"/>
+      <c r="K32" s="516"/>
+      <c r="L32" s="516"/>
+      <c r="M32" s="516"/>
+      <c r="N32" s="516"/>
+      <c r="O32" s="516"/>
     </row>
     <row r="33" spans="3:18">
       <c r="C33" t="s">
@@ -10353,151 +10613,151 @@
       </c>
     </row>
     <row r="34" spans="3:18">
-      <c r="C34" s="515" t="s">
+      <c r="C34" s="516" t="s">
         <v>294</v>
       </c>
-      <c r="D34" s="515"/>
-      <c r="E34" s="515"/>
-      <c r="F34" s="515"/>
-      <c r="G34" s="515"/>
-      <c r="H34" s="515"/>
-      <c r="I34" s="515"/>
-      <c r="J34" s="515"/>
-      <c r="K34" s="515"/>
-      <c r="L34" s="515"/>
-      <c r="M34" s="515"/>
-      <c r="N34" s="515"/>
-      <c r="O34" s="515"/>
-      <c r="P34" s="515"/>
-      <c r="Q34" s="515"/>
-      <c r="R34" s="515"/>
+      <c r="D34" s="516"/>
+      <c r="E34" s="516"/>
+      <c r="F34" s="516"/>
+      <c r="G34" s="516"/>
+      <c r="H34" s="516"/>
+      <c r="I34" s="516"/>
+      <c r="J34" s="516"/>
+      <c r="K34" s="516"/>
+      <c r="L34" s="516"/>
+      <c r="M34" s="516"/>
+      <c r="N34" s="516"/>
+      <c r="O34" s="516"/>
+      <c r="P34" s="516"/>
+      <c r="Q34" s="516"/>
+      <c r="R34" s="516"/>
     </row>
     <row r="35" spans="3:18">
-      <c r="C35" s="515"/>
-      <c r="D35" s="515"/>
-      <c r="E35" s="515"/>
-      <c r="F35" s="515"/>
-      <c r="G35" s="515"/>
-      <c r="H35" s="515"/>
-      <c r="I35" s="515"/>
-      <c r="J35" s="515"/>
-      <c r="K35" s="515"/>
-      <c r="L35" s="515"/>
-      <c r="M35" s="515"/>
-      <c r="N35" s="515"/>
-      <c r="O35" s="515"/>
-      <c r="P35" s="515"/>
-      <c r="Q35" s="515"/>
-      <c r="R35" s="515"/>
+      <c r="C35" s="516"/>
+      <c r="D35" s="516"/>
+      <c r="E35" s="516"/>
+      <c r="F35" s="516"/>
+      <c r="G35" s="516"/>
+      <c r="H35" s="516"/>
+      <c r="I35" s="516"/>
+      <c r="J35" s="516"/>
+      <c r="K35" s="516"/>
+      <c r="L35" s="516"/>
+      <c r="M35" s="516"/>
+      <c r="N35" s="516"/>
+      <c r="O35" s="516"/>
+      <c r="P35" s="516"/>
+      <c r="Q35" s="516"/>
+      <c r="R35" s="516"/>
     </row>
     <row r="36" spans="3:18">
-      <c r="C36" s="515" t="s">
+      <c r="C36" s="516" t="s">
         <v>295</v>
       </c>
-      <c r="D36" s="515"/>
-      <c r="E36" s="515"/>
-      <c r="F36" s="515"/>
-      <c r="G36" s="515"/>
-      <c r="H36" s="515"/>
-      <c r="I36" s="515"/>
-      <c r="J36" s="515"/>
-      <c r="K36" s="515"/>
-      <c r="L36" s="515"/>
-      <c r="M36" s="515"/>
-      <c r="N36" s="515"/>
-      <c r="O36" s="515"/>
+      <c r="D36" s="516"/>
+      <c r="E36" s="516"/>
+      <c r="F36" s="516"/>
+      <c r="G36" s="516"/>
+      <c r="H36" s="516"/>
+      <c r="I36" s="516"/>
+      <c r="J36" s="516"/>
+      <c r="K36" s="516"/>
+      <c r="L36" s="516"/>
+      <c r="M36" s="516"/>
+      <c r="N36" s="516"/>
+      <c r="O36" s="516"/>
     </row>
     <row r="37" spans="3:18">
-      <c r="C37" s="515"/>
-      <c r="D37" s="515"/>
-      <c r="E37" s="515"/>
-      <c r="F37" s="515"/>
-      <c r="G37" s="515"/>
-      <c r="H37" s="515"/>
-      <c r="I37" s="515"/>
-      <c r="J37" s="515"/>
-      <c r="K37" s="515"/>
-      <c r="L37" s="515"/>
-      <c r="M37" s="515"/>
-      <c r="N37" s="515"/>
-      <c r="O37" s="515"/>
+      <c r="C37" s="516"/>
+      <c r="D37" s="516"/>
+      <c r="E37" s="516"/>
+      <c r="F37" s="516"/>
+      <c r="G37" s="516"/>
+      <c r="H37" s="516"/>
+      <c r="I37" s="516"/>
+      <c r="J37" s="516"/>
+      <c r="K37" s="516"/>
+      <c r="L37" s="516"/>
+      <c r="M37" s="516"/>
+      <c r="N37" s="516"/>
+      <c r="O37" s="516"/>
     </row>
     <row r="38" spans="3:18">
-      <c r="C38" s="515" t="s">
+      <c r="C38" s="516" t="s">
         <v>296</v>
       </c>
-      <c r="D38" s="515"/>
-      <c r="E38" s="515"/>
-      <c r="F38" s="515"/>
-      <c r="G38" s="515"/>
-      <c r="H38" s="515"/>
-      <c r="I38" s="515"/>
-      <c r="J38" s="515"/>
-      <c r="K38" s="515"/>
-      <c r="L38" s="515"/>
-      <c r="M38" s="515"/>
-      <c r="N38" s="515"/>
-      <c r="O38" s="515"/>
+      <c r="D38" s="516"/>
+      <c r="E38" s="516"/>
+      <c r="F38" s="516"/>
+      <c r="G38" s="516"/>
+      <c r="H38" s="516"/>
+      <c r="I38" s="516"/>
+      <c r="J38" s="516"/>
+      <c r="K38" s="516"/>
+      <c r="L38" s="516"/>
+      <c r="M38" s="516"/>
+      <c r="N38" s="516"/>
+      <c r="O38" s="516"/>
     </row>
     <row r="39" spans="3:18">
-      <c r="C39" s="515"/>
-      <c r="D39" s="515"/>
-      <c r="E39" s="515"/>
-      <c r="F39" s="515"/>
-      <c r="G39" s="515"/>
-      <c r="H39" s="515"/>
-      <c r="I39" s="515"/>
-      <c r="J39" s="515"/>
-      <c r="K39" s="515"/>
-      <c r="L39" s="515"/>
-      <c r="M39" s="515"/>
-      <c r="N39" s="515"/>
-      <c r="O39" s="515"/>
+      <c r="C39" s="516"/>
+      <c r="D39" s="516"/>
+      <c r="E39" s="516"/>
+      <c r="F39" s="516"/>
+      <c r="G39" s="516"/>
+      <c r="H39" s="516"/>
+      <c r="I39" s="516"/>
+      <c r="J39" s="516"/>
+      <c r="K39" s="516"/>
+      <c r="L39" s="516"/>
+      <c r="M39" s="516"/>
+      <c r="N39" s="516"/>
+      <c r="O39" s="516"/>
     </row>
     <row r="40" spans="3:18">
-      <c r="C40" s="515"/>
-      <c r="D40" s="515"/>
-      <c r="E40" s="515"/>
-      <c r="F40" s="515"/>
-      <c r="G40" s="515"/>
-      <c r="H40" s="515"/>
-      <c r="I40" s="515"/>
-      <c r="J40" s="515"/>
-      <c r="K40" s="515"/>
-      <c r="L40" s="515"/>
-      <c r="M40" s="515"/>
-      <c r="N40" s="515"/>
-      <c r="O40" s="515"/>
+      <c r="C40" s="516"/>
+      <c r="D40" s="516"/>
+      <c r="E40" s="516"/>
+      <c r="F40" s="516"/>
+      <c r="G40" s="516"/>
+      <c r="H40" s="516"/>
+      <c r="I40" s="516"/>
+      <c r="J40" s="516"/>
+      <c r="K40" s="516"/>
+      <c r="L40" s="516"/>
+      <c r="M40" s="516"/>
+      <c r="N40" s="516"/>
+      <c r="O40" s="516"/>
     </row>
     <row r="41" spans="3:18">
-      <c r="C41" s="515"/>
-      <c r="D41" s="515"/>
-      <c r="E41" s="515"/>
-      <c r="F41" s="515"/>
-      <c r="G41" s="515"/>
-      <c r="H41" s="515"/>
-      <c r="I41" s="515"/>
-      <c r="J41" s="515"/>
-      <c r="K41" s="515"/>
-      <c r="L41" s="515"/>
-      <c r="M41" s="515"/>
-      <c r="N41" s="515"/>
-      <c r="O41" s="515"/>
+      <c r="C41" s="516"/>
+      <c r="D41" s="516"/>
+      <c r="E41" s="516"/>
+      <c r="F41" s="516"/>
+      <c r="G41" s="516"/>
+      <c r="H41" s="516"/>
+      <c r="I41" s="516"/>
+      <c r="J41" s="516"/>
+      <c r="K41" s="516"/>
+      <c r="L41" s="516"/>
+      <c r="M41" s="516"/>
+      <c r="N41" s="516"/>
+      <c r="O41" s="516"/>
     </row>
     <row r="42" spans="3:18">
-      <c r="C42" s="515"/>
-      <c r="D42" s="515"/>
-      <c r="E42" s="515"/>
-      <c r="F42" s="515"/>
-      <c r="G42" s="515"/>
-      <c r="H42" s="515"/>
-      <c r="I42" s="515"/>
-      <c r="J42" s="515"/>
-      <c r="K42" s="515"/>
-      <c r="L42" s="515"/>
-      <c r="M42" s="515"/>
-      <c r="N42" s="515"/>
-      <c r="O42" s="515"/>
+      <c r="C42" s="516"/>
+      <c r="D42" s="516"/>
+      <c r="E42" s="516"/>
+      <c r="F42" s="516"/>
+      <c r="G42" s="516"/>
+      <c r="H42" s="516"/>
+      <c r="I42" s="516"/>
+      <c r="J42" s="516"/>
+      <c r="K42" s="516"/>
+      <c r="L42" s="516"/>
+      <c r="M42" s="516"/>
+      <c r="N42" s="516"/>
+      <c r="O42" s="516"/>
     </row>
     <row r="43" spans="3:18">
       <c r="C43" t="s">
@@ -10556,103 +10816,103 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14">
-      <c r="M3" s="491" t="s">
+      <c r="M3" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="N3" s="491"/>
+      <c r="N3" s="492"/>
     </row>
     <row r="4" spans="2:14" ht="26.25">
       <c r="B4" s="338" t="s">
         <v>417</v>
       </c>
-      <c r="M4" s="492"/>
-      <c r="N4" s="492"/>
+      <c r="M4" s="493"/>
+      <c r="N4" s="493"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="515" t="s">
+      <c r="B6" s="516" t="s">
         <v>418</v>
       </c>
-      <c r="C6" s="517"/>
-      <c r="D6" s="517"/>
-      <c r="E6" s="517"/>
-      <c r="F6" s="517"/>
-      <c r="G6" s="517"/>
-      <c r="H6" s="517"/>
-      <c r="I6" s="517"/>
-      <c r="J6" s="517"/>
-      <c r="K6" s="517"/>
+      <c r="C6" s="518"/>
+      <c r="D6" s="518"/>
+      <c r="E6" s="518"/>
+      <c r="F6" s="518"/>
+      <c r="G6" s="518"/>
+      <c r="H6" s="518"/>
+      <c r="I6" s="518"/>
+      <c r="J6" s="518"/>
+      <c r="K6" s="518"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="517"/>
-      <c r="C7" s="517"/>
-      <c r="D7" s="517"/>
-      <c r="E7" s="517"/>
-      <c r="F7" s="517"/>
-      <c r="G7" s="517"/>
-      <c r="H7" s="517"/>
-      <c r="I7" s="517"/>
-      <c r="J7" s="517"/>
-      <c r="K7" s="517"/>
+      <c r="B7" s="518"/>
+      <c r="C7" s="518"/>
+      <c r="D7" s="518"/>
+      <c r="E7" s="518"/>
+      <c r="F7" s="518"/>
+      <c r="G7" s="518"/>
+      <c r="H7" s="518"/>
+      <c r="I7" s="518"/>
+      <c r="J7" s="518"/>
+      <c r="K7" s="518"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="517"/>
-      <c r="C8" s="517"/>
-      <c r="D8" s="517"/>
-      <c r="E8" s="517"/>
-      <c r="F8" s="517"/>
-      <c r="G8" s="517"/>
-      <c r="H8" s="517"/>
-      <c r="I8" s="517"/>
-      <c r="J8" s="517"/>
-      <c r="K8" s="517"/>
+      <c r="B8" s="518"/>
+      <c r="C8" s="518"/>
+      <c r="D8" s="518"/>
+      <c r="E8" s="518"/>
+      <c r="F8" s="518"/>
+      <c r="G8" s="518"/>
+      <c r="H8" s="518"/>
+      <c r="I8" s="518"/>
+      <c r="J8" s="518"/>
+      <c r="K8" s="518"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="517"/>
-      <c r="C9" s="517"/>
-      <c r="D9" s="517"/>
-      <c r="E9" s="517"/>
-      <c r="F9" s="517"/>
-      <c r="G9" s="517"/>
-      <c r="H9" s="517"/>
-      <c r="I9" s="517"/>
-      <c r="J9" s="517"/>
-      <c r="K9" s="517"/>
+      <c r="B9" s="518"/>
+      <c r="C9" s="518"/>
+      <c r="D9" s="518"/>
+      <c r="E9" s="518"/>
+      <c r="F9" s="518"/>
+      <c r="G9" s="518"/>
+      <c r="H9" s="518"/>
+      <c r="I9" s="518"/>
+      <c r="J9" s="518"/>
+      <c r="K9" s="518"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="B10" s="517"/>
-      <c r="C10" s="517"/>
-      <c r="D10" s="517"/>
-      <c r="E10" s="517"/>
-      <c r="F10" s="517"/>
-      <c r="G10" s="517"/>
-      <c r="H10" s="517"/>
-      <c r="I10" s="517"/>
-      <c r="J10" s="517"/>
-      <c r="K10" s="517"/>
+      <c r="B10" s="518"/>
+      <c r="C10" s="518"/>
+      <c r="D10" s="518"/>
+      <c r="E10" s="518"/>
+      <c r="F10" s="518"/>
+      <c r="G10" s="518"/>
+      <c r="H10" s="518"/>
+      <c r="I10" s="518"/>
+      <c r="J10" s="518"/>
+      <c r="K10" s="518"/>
     </row>
     <row r="11" spans="2:14" ht="2.1" customHeight="1">
-      <c r="B11" s="517"/>
-      <c r="C11" s="517"/>
-      <c r="D11" s="517"/>
-      <c r="E11" s="517"/>
-      <c r="F11" s="517"/>
-      <c r="G11" s="517"/>
-      <c r="H11" s="517"/>
-      <c r="I11" s="517"/>
-      <c r="J11" s="517"/>
-      <c r="K11" s="517"/>
+      <c r="B11" s="518"/>
+      <c r="C11" s="518"/>
+      <c r="D11" s="518"/>
+      <c r="E11" s="518"/>
+      <c r="F11" s="518"/>
+      <c r="G11" s="518"/>
+      <c r="H11" s="518"/>
+      <c r="I11" s="518"/>
+      <c r="J11" s="518"/>
+      <c r="K11" s="518"/>
     </row>
     <row r="12" spans="2:14" hidden="1">
-      <c r="B12" s="517"/>
-      <c r="C12" s="517"/>
-      <c r="D12" s="517"/>
-      <c r="E12" s="517"/>
-      <c r="F12" s="517"/>
-      <c r="G12" s="517"/>
-      <c r="H12" s="517"/>
-      <c r="I12" s="517"/>
-      <c r="J12" s="517"/>
-      <c r="K12" s="517"/>
+      <c r="B12" s="518"/>
+      <c r="C12" s="518"/>
+      <c r="D12" s="518"/>
+      <c r="E12" s="518"/>
+      <c r="F12" s="518"/>
+      <c r="G12" s="518"/>
+      <c r="H12" s="518"/>
+      <c r="I12" s="518"/>
+      <c r="J12" s="518"/>
+      <c r="K12" s="518"/>
     </row>
     <row r="14" spans="2:14" ht="48" thickBot="1">
       <c r="C14" s="236" t="s">
@@ -10754,14 +11014,14 @@
       <c r="B2" s="480" t="s">
         <v>252</v>
       </c>
-      <c r="I2" s="491" t="s">
+      <c r="I2" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="J2" s="491"/>
+      <c r="J2" s="492"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="I3" s="492"/>
-      <c r="J3" s="492"/>
+      <c r="I3" s="493"/>
+      <c r="J3" s="493"/>
     </row>
     <row r="4" spans="2:10">
       <c r="B4" s="142" t="s">
@@ -10823,14 +11083,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
-      <c r="I2" s="491" t="s">
+      <c r="I2" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="J2" s="491"/>
+      <c r="J2" s="492"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="I3" s="492"/>
-      <c r="J3" s="492"/>
+      <c r="I3" s="493"/>
+      <c r="J3" s="493"/>
     </row>
     <row r="5" spans="2:10" ht="23.25">
       <c r="B5" s="480" t="s">
@@ -10853,11 +11113,11 @@
       </c>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="518" t="s">
+      <c r="B12" s="519" t="s">
         <v>548</v>
       </c>
-      <c r="C12" s="518"/>
-      <c r="D12" s="518"/>
+      <c r="C12" s="519"/>
+      <c r="D12" s="519"/>
     </row>
     <row r="13" spans="2:10" ht="33.950000000000003" customHeight="1">
       <c r="B13" s="198" t="s">
@@ -11134,14 +11394,14 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14">
-      <c r="M3" s="491" t="s">
+      <c r="M3" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="N3" s="491"/>
+      <c r="N3" s="492"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="M4" s="492"/>
-      <c r="N4" s="492"/>
+      <c r="M4" s="493"/>
+      <c r="N4" s="493"/>
     </row>
     <row r="5" spans="2:14" ht="23.25">
       <c r="B5" s="480" t="s">
@@ -11164,11 +11424,11 @@
       </c>
     </row>
     <row r="12" spans="2:14">
-      <c r="B12" s="518" t="s">
+      <c r="B12" s="519" t="s">
         <v>548</v>
       </c>
-      <c r="C12" s="518"/>
-      <c r="D12" s="518"/>
+      <c r="C12" s="519"/>
+      <c r="D12" s="519"/>
     </row>
     <row r="13" spans="2:14">
       <c r="B13" s="198" t="s">
@@ -11444,14 +11704,14 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="2" spans="15:16">
-      <c r="O2" s="491" t="s">
+      <c r="O2" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="P2" s="491"/>
+      <c r="P2" s="492"/>
     </row>
     <row r="3" spans="15:16">
-      <c r="O3" s="492"/>
-      <c r="P3" s="492"/>
+      <c r="O3" s="493"/>
+      <c r="P3" s="493"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -13780,10 +14040,10 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="L6" s="491" t="s">
+      <c r="L6" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="M6" s="491"/>
+      <c r="M6" s="492"/>
     </row>
     <row r="7" spans="1:13" ht="24" customHeight="1">
       <c r="A7" s="9" t="s">
@@ -13802,8 +14062,8 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
-      <c r="L7" s="492"/>
-      <c r="M7" s="492"/>
+      <c r="L7" s="493"/>
+      <c r="M7" s="493"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="358" t="s">
@@ -14774,10 +15034,10 @@
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
-      <c r="E53" s="489" t="s">
+      <c r="E53" s="490" t="s">
         <v>471</v>
       </c>
-      <c r="F53" s="489"/>
+      <c r="F53" s="490"/>
       <c r="G53" s="372">
         <v>143</v>
       </c>
@@ -14794,8 +15054,8 @@
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
-      <c r="E54" s="490"/>
-      <c r="F54" s="490"/>
+      <c r="E54" s="491"/>
+      <c r="F54" s="491"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
@@ -15214,18 +15474,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="493" t="s">
+      <c r="A1" s="494" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="493"/>
-      <c r="C1" s="493"/>
-      <c r="D1" s="493"/>
-      <c r="E1" s="493"/>
-      <c r="F1" s="493"/>
-      <c r="G1" s="493"/>
-      <c r="H1" s="493"/>
-      <c r="I1" s="493"/>
-      <c r="J1" s="493"/>
+      <c r="B1" s="494"/>
+      <c r="C1" s="494"/>
+      <c r="D1" s="494"/>
+      <c r="E1" s="494"/>
+      <c r="F1" s="494"/>
+      <c r="G1" s="494"/>
+      <c r="H1" s="494"/>
+      <c r="I1" s="494"/>
+      <c r="J1" s="494"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
@@ -15292,10 +15552,10 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="L6" s="491" t="s">
+      <c r="L6" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="M6" s="491"/>
+      <c r="M6" s="492"/>
     </row>
     <row r="7" spans="1:13" ht="15.95" customHeight="1">
       <c r="A7" s="9" t="s">
@@ -15314,8 +15574,8 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
-      <c r="L7" s="492"/>
-      <c r="M7" s="492"/>
+      <c r="L7" s="493"/>
+      <c r="M7" s="493"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="358" t="s">
@@ -16394,10 +16654,10 @@
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
-      <c r="E54" s="489" t="s">
+      <c r="E54" s="490" t="s">
         <v>472</v>
       </c>
-      <c r="F54" s="489"/>
+      <c r="F54" s="490"/>
       <c r="G54" s="375">
         <v>143</v>
       </c>
@@ -16417,8 +16677,8 @@
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
-      <c r="E55" s="490"/>
-      <c r="F55" s="490"/>
+      <c r="E55" s="491"/>
+      <c r="F55" s="491"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
@@ -16807,7 +17067,7 @@
     <row r="77" spans="1:10">
       <c r="A77" s="86">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45857</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -17873,10 +18133,10 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="491" t="s">
+      <c r="L7" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="M7" s="491"/>
+      <c r="M7" s="492"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="358" t="s">
@@ -17898,8 +18158,8 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="8"/>
-      <c r="L8" s="492"/>
-      <c r="M8" s="492"/>
+      <c r="L8" s="493"/>
+      <c r="M8" s="493"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="14"/>
@@ -18932,10 +19192,10 @@
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
-      <c r="E51" s="489" t="s">
+      <c r="E51" s="490" t="s">
         <v>472</v>
       </c>
-      <c r="F51" s="489"/>
+      <c r="F51" s="490"/>
       <c r="G51" s="375">
         <v>143</v>
       </c>
@@ -18955,8 +19215,8 @@
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
-      <c r="E52" s="490"/>
-      <c r="F52" s="490"/>
+      <c r="E52" s="491"/>
+      <c r="F52" s="491"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -19250,11 +19510,11 @@
       </c>
     </row>
     <row r="70" spans="1:11" ht="48" customHeight="1">
-      <c r="A70" s="494" t="s">
+      <c r="A70" s="495" t="s">
         <v>311</v>
       </c>
-      <c r="B70" s="494"/>
-      <c r="C70" s="494"/>
+      <c r="B70" s="495"/>
+      <c r="C70" s="495"/>
       <c r="D70" s="240"/>
       <c r="E70" s="241"/>
       <c r="F70" s="241"/>
@@ -19275,11 +19535,11 @@
       <c r="F71" s="246" t="s">
         <v>27</v>
       </c>
-      <c r="G71" s="495" t="s">
+      <c r="G71" s="496" t="s">
         <v>77</v>
       </c>
-      <c r="H71" s="495"/>
-      <c r="I71" s="495"/>
+      <c r="H71" s="496"/>
+      <c r="I71" s="496"/>
     </row>
     <row r="72" spans="1:11" ht="35.1" customHeight="1">
       <c r="A72" s="235" t="s">
@@ -19301,11 +19561,11 @@
       <c r="F72" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="G72" s="497" t="s">
+      <c r="G72" s="498" t="s">
         <v>306</v>
       </c>
-      <c r="H72" s="497"/>
-      <c r="I72" s="497"/>
+      <c r="H72" s="498"/>
+      <c r="I72" s="498"/>
     </row>
     <row r="73" spans="1:11" ht="45" customHeight="1">
       <c r="A73" s="235" t="s">
@@ -19326,11 +19586,11 @@
       <c r="F73" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="G73" s="497" t="s">
+      <c r="G73" s="498" t="s">
         <v>308</v>
       </c>
-      <c r="H73" s="497"/>
-      <c r="I73" s="497"/>
+      <c r="H73" s="498"/>
+      <c r="I73" s="498"/>
     </row>
     <row r="74" spans="1:11" ht="74.099999999999994" customHeight="1">
       <c r="A74" s="247" t="s">
@@ -19349,11 +19609,11 @@
       <c r="F74" s="250" t="s">
         <v>305</v>
       </c>
-      <c r="G74" s="496" t="s">
+      <c r="G74" s="497" t="s">
         <v>310</v>
       </c>
-      <c r="H74" s="496"/>
-      <c r="I74" s="496"/>
+      <c r="H74" s="497"/>
+      <c r="I74" s="497"/>
     </row>
     <row r="75" spans="1:11">
       <c r="E75" s="169">
@@ -19530,7 +19790,7 @@
     <row r="101" spans="1:11">
       <c r="A101" s="86">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45857</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -19659,10 +19919,10 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="8"/>
-      <c r="L6" s="491" t="s">
+      <c r="L6" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="M6" s="491"/>
+      <c r="M6" s="492"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="9" t="s">
@@ -19682,8 +19942,8 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="492"/>
-      <c r="M7" s="492"/>
+      <c r="L7" s="493"/>
+      <c r="M7" s="493"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="358" t="s">
@@ -20720,10 +20980,10 @@
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
-      <c r="E51" s="489" t="s">
+      <c r="E51" s="490" t="s">
         <v>472</v>
       </c>
-      <c r="F51" s="489"/>
+      <c r="F51" s="490"/>
       <c r="G51" s="375">
         <v>143</v>
       </c>
@@ -20743,8 +21003,8 @@
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
-      <c r="E52" s="490"/>
-      <c r="F52" s="490"/>
+      <c r="E52" s="491"/>
+      <c r="F52" s="491"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -21140,7 +21400,7 @@
     <row r="73" spans="1:11">
       <c r="A73" s="86">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45857</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -21328,10 +21588,10 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="8"/>
-      <c r="L6" s="491" t="s">
+      <c r="L6" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="M6" s="491"/>
+      <c r="M6" s="492"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="9" t="s">
@@ -21351,8 +21611,8 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="492"/>
-      <c r="M7" s="492"/>
+      <c r="L7" s="493"/>
+      <c r="M7" s="493"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="358" t="s">
@@ -22340,10 +22600,10 @@
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
-      <c r="E49" s="489" t="s">
+      <c r="E49" s="490" t="s">
         <v>472</v>
       </c>
-      <c r="F49" s="489"/>
+      <c r="F49" s="490"/>
       <c r="G49" s="375">
         <v>143</v>
       </c>
@@ -22363,8 +22623,8 @@
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
-      <c r="E50" s="490"/>
-      <c r="F50" s="490"/>
+      <c r="E50" s="491"/>
+      <c r="F50" s="491"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -22653,11 +22913,11 @@
       <c r="K63" s="8"/>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" s="498" t="s">
+      <c r="A65" s="499" t="s">
         <v>311</v>
       </c>
-      <c r="B65" s="498"/>
-      <c r="C65" s="498"/>
+      <c r="B65" s="499"/>
+      <c r="C65" s="499"/>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="244"/>
@@ -22674,11 +22934,11 @@
       <c r="F66" s="246" t="s">
         <v>27</v>
       </c>
-      <c r="G66" s="495" t="s">
+      <c r="G66" s="496" t="s">
         <v>77</v>
       </c>
-      <c r="H66" s="495"/>
-      <c r="I66" s="495"/>
+      <c r="H66" s="496"/>
+      <c r="I66" s="496"/>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="235" t="s">
@@ -22700,11 +22960,11 @@
       <c r="F67" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="G67" s="497" t="s">
+      <c r="G67" s="498" t="s">
         <v>306</v>
       </c>
-      <c r="H67" s="497"/>
-      <c r="I67" s="497"/>
+      <c r="H67" s="498"/>
+      <c r="I67" s="498"/>
     </row>
     <row r="68" spans="1:11" ht="41.1" customHeight="1">
       <c r="A68" s="235" t="s">
@@ -22725,11 +22985,11 @@
       <c r="F68" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="G68" s="497" t="s">
+      <c r="G68" s="498" t="s">
         <v>308</v>
       </c>
-      <c r="H68" s="497"/>
-      <c r="I68" s="497"/>
+      <c r="H68" s="498"/>
+      <c r="I68" s="498"/>
     </row>
     <row r="69" spans="1:11" ht="81" customHeight="1">
       <c r="A69" s="247" t="s">
@@ -22748,11 +23008,11 @@
       <c r="F69" s="250" t="s">
         <v>305</v>
       </c>
-      <c r="G69" s="496" t="s">
+      <c r="G69" s="497" t="s">
         <v>310</v>
       </c>
-      <c r="H69" s="496"/>
-      <c r="I69" s="496"/>
+      <c r="H69" s="497"/>
+      <c r="I69" s="497"/>
     </row>
     <row r="70" spans="1:11">
       <c r="E70" s="169">
@@ -22914,7 +23174,7 @@
     <row r="88" spans="1:11">
       <c r="A88" s="86">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45857</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -23075,10 +23335,10 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="491" t="s">
+      <c r="K5" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="L5" s="491"/>
+      <c r="L5" s="492"/>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="8"/>
@@ -23091,8 +23351,8 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="492"/>
-      <c r="L6" s="492"/>
+      <c r="K6" s="493"/>
+      <c r="L6" s="493"/>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="9" t="s">
@@ -25891,7 +26151,7 @@
     <row r="133" spans="1:11">
       <c r="A133" s="86">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45857</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -26044,10 +26304,10 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="8"/>
-      <c r="L6" s="491" t="s">
+      <c r="L6" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="M6" s="491"/>
+      <c r="M6" s="492"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="9" t="s">
@@ -26065,8 +26325,8 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="492"/>
-      <c r="M7" s="492"/>
+      <c r="L7" s="493"/>
+      <c r="M7" s="493"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="358" t="s">
@@ -28634,7 +28894,7 @@
         <f>((H113*H79)+H70)/(D9+(C80*C79))</f>
         <v>26.401052631578946</v>
       </c>
-      <c r="I120" s="519">
+      <c r="I120" s="487">
         <f>((I113*H79)+I70)/(D9+(C80*C79))</f>
         <v>63.445185824561399</v>
       </c>
@@ -28849,7 +29109,7 @@
     <row r="133" spans="1:11">
       <c r="A133" s="86">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45857</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -29307,10 +29567,10 @@
         <v>385</v>
       </c>
       <c r="F2" s="236"/>
-      <c r="N2" s="491" t="s">
+      <c r="N2" s="492" t="s">
         <v>549</v>
       </c>
-      <c r="O2" s="491"/>
+      <c r="O2" s="492"/>
     </row>
     <row r="3" spans="1:18" ht="42" customHeight="1" thickBot="1">
       <c r="A3" s="251" t="s">
@@ -29328,27 +29588,27 @@
       <c r="K3" s="88"/>
       <c r="L3" s="88"/>
       <c r="M3" s="88"/>
-      <c r="N3" s="492"/>
-      <c r="O3" s="492"/>
+      <c r="N3" s="493"/>
+      <c r="O3" s="493"/>
       <c r="P3" s="88"/>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>324</v>
       </c>
-      <c r="F4" s="499" t="s">
+      <c r="F4" s="500" t="s">
         <v>325</v>
       </c>
-      <c r="G4" s="499"/>
-      <c r="H4" s="499"/>
-      <c r="I4" s="499"/>
-      <c r="J4" s="499"/>
-      <c r="K4" s="499"/>
-      <c r="L4" s="499"/>
-      <c r="M4" s="499"/>
-      <c r="N4" s="499"/>
-      <c r="O4" s="499"/>
-      <c r="P4" s="499"/>
+      <c r="G4" s="500"/>
+      <c r="H4" s="500"/>
+      <c r="I4" s="500"/>
+      <c r="J4" s="500"/>
+      <c r="K4" s="500"/>
+      <c r="L4" s="500"/>
+      <c r="M4" s="500"/>
+      <c r="N4" s="500"/>
+      <c r="O4" s="500"/>
+      <c r="P4" s="500"/>
     </row>
     <row r="5" spans="1:18" ht="32.25" thickBot="1">
       <c r="A5" s="253"/>

--- a/PEWI Budgets 2024$ - 2025$ (021425).xlsx
+++ b/PEWI Budgets 2024$ - 2025$ (021425).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_pewi\PEWI-People-in-Ecosystem-and-Watershed-Integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882B919A-B065-496D-8BE9-D3E793EF560B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D18FFD-D5DB-4567-8F97-CBB1B2BA830D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2A59C1DF-064D-264D-B5F5-440AD859B569}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="581">
   <si>
     <t>Ag Decision Maker -- Iowa State University Extension and Outreach</t>
   </si>
@@ -2186,6 +2186,24 @@
       </rPr>
       <t>−1</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kg </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>−1</t>
+    </r>
+  </si>
+  <si>
+    <t>Kg −1</t>
   </si>
 </sst>
 </file>
@@ -5914,7 +5932,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="43" spans="2:4">
+    <row r="43" spans="2:4" ht="16.5" thickBot="1">
       <c r="B43" t="s">
         <v>572</v>
       </c>
@@ -5930,7 +5948,10 @@
         <v>463</v>
       </c>
       <c r="C44">
-        <v>5.65</v>
+        <v>12.46</v>
+      </c>
+      <c r="D44" s="520" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="45" spans="2:4">
@@ -5938,7 +5959,10 @@
         <v>464</v>
       </c>
       <c r="C45">
-        <v>5.65</v>
+        <v>12.46</v>
+      </c>
+      <c r="D45" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="46" spans="2:4">

--- a/PEWI Budgets 2024$ - 2025$ (021425).xlsx
+++ b/PEWI Budgets 2024$ - 2025$ (021425).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_pewi\PEWI-People-in-Ecosystem-and-Watershed-Integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D18FFD-D5DB-4567-8F97-CBB1B2BA830D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4508143-4D74-46FC-B54E-A32215842C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2A59C1DF-064D-264D-B5F5-440AD859B569}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18240" activeTab="2" xr2:uid="{2A59C1DF-064D-264D-B5F5-440AD859B569}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions &amp; summary data" sheetId="19" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="583">
   <si>
     <t>Ag Decision Maker -- Iowa State University Extension and Outreach</t>
   </si>
@@ -2140,31 +2140,13 @@
     <t>500 Acres</t>
   </si>
   <si>
-    <t>Land use</t>
-  </si>
-  <si>
-    <t>Unit price</t>
-  </si>
-  <si>
     <t>Source</t>
   </si>
   <si>
-    <t>Conventional Soybean</t>
-  </si>
-  <si>
     <t>Switchgrass Bioenergy</t>
   </si>
   <si>
     <t>Short-Rotation Woody Biomass</t>
-  </si>
-  <si>
-    <t>Soybean following Corn</t>
-  </si>
-  <si>
-    <t>Corn following Soybean</t>
-  </si>
-  <si>
-    <t>Corn following Corn</t>
   </si>
   <si>
     <t>Carbon Credit</t>
@@ -2203,7 +2185,43 @@
     </r>
   </si>
   <si>
-    <t>Kg −1</t>
+    <r>
+      <t xml:space="preserve">Acre </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>−1</t>
+    </r>
+  </si>
+  <si>
+    <t>(Johanns, 2024)</t>
+  </si>
+  <si>
+    <t>Land Use Category</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Conventional Corn following Corn</t>
+  </si>
+  <si>
+    <t>Convenetional Corn following Soybean</t>
+  </si>
+  <si>
+    <t>Conventional Soybean following Corn</t>
+  </si>
+  <si>
+    <t>Conventional Conservation Corn</t>
+  </si>
+  <si>
+    <t>USDA, 2025</t>
   </si>
 </sst>
 </file>
@@ -5323,7 +5341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE1E20D6-F156-C447-BE27-5EDB562A8E09}">
-  <dimension ref="B2:M51"/>
+  <dimension ref="B2:M49"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -5820,194 +5838,220 @@
         <v>512</v>
       </c>
     </row>
-    <row r="32" spans="2:9">
+    <row r="32" spans="2:9" ht="16.5" thickBot="1">
       <c r="B32" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="C32" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="D32" t="s">
         <v>183</v>
       </c>
       <c r="E32" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" ht="16.5" thickBot="1">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="16.5" thickBot="1">
       <c r="B33" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" ht="16.5" thickBot="1">
+        <v>578</v>
+      </c>
+      <c r="C33">
+        <v>171.23</v>
+      </c>
+      <c r="D33" s="520" t="s">
+        <v>572</v>
+      </c>
+      <c r="E33" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" ht="16.5" thickBot="1">
       <c r="B34" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C34">
         <v>171.23</v>
       </c>
       <c r="D34" s="520" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4">
+        <v>572</v>
+      </c>
+      <c r="E34" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="16.5" thickBot="1">
       <c r="B35" t="s">
+        <v>580</v>
+      </c>
+      <c r="C35">
+        <v>381.07</v>
+      </c>
+      <c r="D35" s="520" t="s">
+        <v>572</v>
+      </c>
+      <c r="E35" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" ht="16.5" thickBot="1">
+      <c r="B36" t="s">
+        <v>581</v>
+      </c>
+      <c r="C36">
+        <v>171.23</v>
+      </c>
+      <c r="D36" s="520" t="s">
+        <v>572</v>
+      </c>
+      <c r="E36" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="16.5" thickBot="1">
+      <c r="B37" t="s">
+        <v>458</v>
+      </c>
+      <c r="C37">
+        <v>481.29</v>
+      </c>
+      <c r="D37" s="520" t="s">
+        <v>572</v>
+      </c>
+      <c r="E37" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="16.5" thickBot="1">
+      <c r="B38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38">
+        <v>253</v>
+      </c>
+      <c r="D38" s="520" t="s">
+        <v>572</v>
+      </c>
+      <c r="E38" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" ht="16.5" thickBot="1">
+      <c r="B39" t="s">
+        <v>473</v>
+      </c>
+      <c r="C39">
+        <v>180</v>
+      </c>
+      <c r="D39" s="520" t="s">
+        <v>572</v>
+      </c>
+      <c r="E39" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="16.5" thickBot="1">
+      <c r="B40" t="s">
+        <v>568</v>
+      </c>
+      <c r="C40">
+        <v>60</v>
+      </c>
+      <c r="D40" s="520" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" ht="16.5" thickBot="1">
+      <c r="B41" t="s">
+        <v>569</v>
+      </c>
+      <c r="C41">
+        <v>60</v>
+      </c>
+      <c r="D41" s="520" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" ht="16.5" thickBot="1">
+      <c r="B42" t="s">
+        <v>463</v>
+      </c>
+      <c r="C42">
+        <v>12.46</v>
+      </c>
+      <c r="D42" s="520" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5">
+      <c r="B43" t="s">
+        <v>464</v>
+      </c>
+      <c r="C43">
+        <v>12.46</v>
+      </c>
+      <c r="D43" s="520" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5">
+      <c r="B44" t="s">
+        <v>469</v>
+      </c>
+      <c r="C44">
+        <v>0.79</v>
+      </c>
+      <c r="D44" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" ht="16.5" thickBot="1">
+      <c r="B45" t="s">
+        <v>470</v>
+      </c>
+      <c r="C45">
+        <v>0.79</v>
+      </c>
+      <c r="D45" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" ht="16.5" thickBot="1">
+      <c r="B46" t="s">
+        <v>570</v>
+      </c>
+      <c r="C46">
+        <v>40.82</v>
+      </c>
+      <c r="D46" s="520" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" ht="16.5" thickBot="1">
+      <c r="B47" t="s">
+        <v>467</v>
+      </c>
+      <c r="C47">
+        <v>205</v>
+      </c>
+      <c r="D47" s="520" t="s">
         <v>574</v>
       </c>
-      <c r="C35">
-        <v>171.23</v>
-      </c>
-      <c r="D35" s="520" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" ht="16.5" thickBot="1">
-      <c r="B36" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" ht="16.5" thickBot="1">
-      <c r="B37" t="s">
-        <v>573</v>
-      </c>
-      <c r="C37">
-        <v>381.07</v>
-      </c>
-      <c r="D37" s="520" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" ht="16.5" thickBot="1">
-      <c r="B38" t="s">
-        <v>456</v>
-      </c>
-      <c r="C38">
-        <v>171.23</v>
-      </c>
-      <c r="D38" s="520" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" ht="16.5" thickBot="1">
-      <c r="B39" t="s">
-        <v>458</v>
-      </c>
-      <c r="C39">
-        <v>481.29</v>
-      </c>
-      <c r="D39" s="520" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" ht="16.5" thickBot="1">
-      <c r="B40" t="s">
-        <v>131</v>
-      </c>
-      <c r="C40">
-        <v>253</v>
-      </c>
-      <c r="D40" s="520" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" ht="16.5" thickBot="1">
-      <c r="B41" t="s">
-        <v>473</v>
-      </c>
-      <c r="C41">
-        <v>180</v>
-      </c>
-      <c r="D41" s="520" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" ht="16.5" thickBot="1">
-      <c r="B42" t="s">
+    </row>
+    <row r="48" spans="2:5">
+      <c r="B48" t="s">
+        <v>468</v>
+      </c>
+      <c r="C48">
+        <v>312.08999999999997</v>
+      </c>
+      <c r="D48" s="520" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" t="s">
         <v>571</v>
-      </c>
-      <c r="C42">
-        <v>60</v>
-      </c>
-      <c r="D42" s="520" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" ht="16.5" thickBot="1">
-      <c r="B43" t="s">
-        <v>572</v>
-      </c>
-      <c r="C43">
-        <v>60</v>
-      </c>
-      <c r="D43" s="520" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4">
-      <c r="B44" t="s">
-        <v>463</v>
-      </c>
-      <c r="C44">
-        <v>12.46</v>
-      </c>
-      <c r="D44" s="520" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4">
-      <c r="B45" t="s">
-        <v>464</v>
-      </c>
-      <c r="C45">
-        <v>12.46</v>
-      </c>
-      <c r="D45" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4">
-      <c r="B46" t="s">
-        <v>469</v>
-      </c>
-      <c r="C46">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4">
-      <c r="B47" t="s">
-        <v>470</v>
-      </c>
-      <c r="C47">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4">
-      <c r="B48" t="s">
-        <v>576</v>
-      </c>
-      <c r="C48">
-        <v>40.82</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3">
-      <c r="B49" t="s">
-        <v>467</v>
-      </c>
-      <c r="C49">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3">
-      <c r="B50" t="s">
-        <v>468</v>
-      </c>
-      <c r="C50">
-        <v>312.08999999999997</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3">
-      <c r="B51" t="s">
-        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -17091,7 +17135,7 @@
     <row r="77" spans="1:10">
       <c r="A77" s="86">
         <f ca="1">TODAY()</f>
-        <v>45857</v>
+        <v>45859</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -19814,7 +19858,7 @@
     <row r="101" spans="1:11">
       <c r="A101" s="86">
         <f ca="1">TODAY()</f>
-        <v>45857</v>
+        <v>45859</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -21424,7 +21468,7 @@
     <row r="73" spans="1:11">
       <c r="A73" s="86">
         <f ca="1">TODAY()</f>
-        <v>45857</v>
+        <v>45859</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -23198,7 +23242,7 @@
     <row r="88" spans="1:11">
       <c r="A88" s="86">
         <f ca="1">TODAY()</f>
-        <v>45857</v>
+        <v>45859</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -26175,7 +26219,7 @@
     <row r="133" spans="1:11">
       <c r="A133" s="86">
         <f ca="1">TODAY()</f>
-        <v>45857</v>
+        <v>45859</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -29133,7 +29177,7 @@
     <row r="133" spans="1:11">
       <c r="A133" s="86">
         <f ca="1">TODAY()</f>
-        <v>45857</v>
+        <v>45859</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>

--- a/PEWI Budgets 2024$ - 2025$ (021425).xlsx
+++ b/PEWI Budgets 2024$ - 2025$ (021425).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_pewi\PEWI-People-in-Ecosystem-and-Watershed-Integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4508143-4D74-46FC-B54E-A32215842C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F4A016-C6CD-4F63-BFCC-FC07113D4CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18240" activeTab="2" xr2:uid="{2A59C1DF-064D-264D-B5F5-440AD859B569}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="4" xr2:uid="{2A59C1DF-064D-264D-B5F5-440AD859B569}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions &amp; summary data" sheetId="19" r:id="rId1"/>
@@ -4395,6 +4395,9 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="51" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4443,6 +4446,15 @@
     <xf numFmtId="44" fontId="0" fillId="12" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4464,21 +4476,12 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4490,9 +4493,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -5374,20 +5374,20 @@
       <c r="E4" s="454" t="s">
         <v>485</v>
       </c>
-      <c r="F4" s="488" t="s">
+      <c r="F4" s="489" t="s">
         <v>480</v>
       </c>
-      <c r="G4" s="488"/>
+      <c r="G4" s="489"/>
       <c r="H4" s="454" t="s">
         <v>545</v>
       </c>
-      <c r="I4" s="489" t="s">
+      <c r="I4" s="490" t="s">
         <v>77</v>
       </c>
-      <c r="J4" s="489"/>
-      <c r="K4" s="489"/>
-      <c r="L4" s="489"/>
-      <c r="M4" s="489"/>
+      <c r="J4" s="490"/>
+      <c r="K4" s="490"/>
+      <c r="L4" s="490"/>
+      <c r="M4" s="490"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" t="s">
@@ -5859,7 +5859,7 @@
       <c r="C33">
         <v>171.23</v>
       </c>
-      <c r="D33" s="520" t="s">
+      <c r="D33" s="488" t="s">
         <v>572</v>
       </c>
       <c r="E33" t="s">
@@ -5873,7 +5873,7 @@
       <c r="C34">
         <v>171.23</v>
       </c>
-      <c r="D34" s="520" t="s">
+      <c r="D34" s="488" t="s">
         <v>572</v>
       </c>
       <c r="E34" t="s">
@@ -5887,7 +5887,7 @@
       <c r="C35">
         <v>381.07</v>
       </c>
-      <c r="D35" s="520" t="s">
+      <c r="D35" s="488" t="s">
         <v>572</v>
       </c>
       <c r="E35" t="s">
@@ -5901,7 +5901,7 @@
       <c r="C36">
         <v>171.23</v>
       </c>
-      <c r="D36" s="520" t="s">
+      <c r="D36" s="488" t="s">
         <v>572</v>
       </c>
       <c r="E36" t="s">
@@ -5915,7 +5915,7 @@
       <c r="C37">
         <v>481.29</v>
       </c>
-      <c r="D37" s="520" t="s">
+      <c r="D37" s="488" t="s">
         <v>572</v>
       </c>
       <c r="E37" t="s">
@@ -5929,7 +5929,7 @@
       <c r="C38">
         <v>253</v>
       </c>
-      <c r="D38" s="520" t="s">
+      <c r="D38" s="488" t="s">
         <v>572</v>
       </c>
       <c r="E38" t="s">
@@ -5943,7 +5943,7 @@
       <c r="C39">
         <v>180</v>
       </c>
-      <c r="D39" s="520" t="s">
+      <c r="D39" s="488" t="s">
         <v>572</v>
       </c>
       <c r="E39" t="s">
@@ -5957,7 +5957,7 @@
       <c r="C40">
         <v>60</v>
       </c>
-      <c r="D40" s="520" t="s">
+      <c r="D40" s="488" t="s">
         <v>572</v>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       <c r="C41">
         <v>60</v>
       </c>
-      <c r="D41" s="520" t="s">
+      <c r="D41" s="488" t="s">
         <v>572</v>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       <c r="C42">
         <v>12.46</v>
       </c>
-      <c r="D42" s="520" t="s">
+      <c r="D42" s="488" t="s">
         <v>573</v>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       <c r="C43">
         <v>12.46</v>
       </c>
-      <c r="D43" s="520" t="s">
+      <c r="D43" s="488" t="s">
         <v>573</v>
       </c>
     </row>
@@ -6023,7 +6023,7 @@
       <c r="C46">
         <v>40.82</v>
       </c>
-      <c r="D46" s="520" t="s">
+      <c r="D46" s="488" t="s">
         <v>572</v>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       <c r="C47">
         <v>205</v>
       </c>
-      <c r="D47" s="520" t="s">
+      <c r="D47" s="488" t="s">
         <v>574</v>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       <c r="C48">
         <v>312.08999999999997</v>
       </c>
-      <c r="D48" s="520" t="s">
+      <c r="D48" s="488" t="s">
         <v>574</v>
       </c>
     </row>
@@ -6617,14 +6617,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24">
-      <c r="M2" s="492" t="s">
+      <c r="M2" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="N2" s="492"/>
+      <c r="N2" s="493"/>
     </row>
     <row r="3" spans="1:24" ht="16.5" thickBot="1">
-      <c r="M3" s="493"/>
-      <c r="N3" s="493"/>
+      <c r="M3" s="494"/>
+      <c r="N3" s="494"/>
     </row>
     <row r="4" spans="1:24" ht="16.5" thickBot="1">
       <c r="A4" s="347" t="s">
@@ -8415,71 +8415,71 @@
       </c>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="501" t="s">
+      <c r="A57" s="502" t="s">
         <v>551</v>
       </c>
-      <c r="B57" s="501"/>
-      <c r="C57" s="501"/>
-      <c r="D57" s="501"/>
-      <c r="E57" s="501"/>
-      <c r="F57" s="501"/>
-      <c r="G57" s="501"/>
-      <c r="H57" s="501"/>
-      <c r="I57" s="501"/>
-      <c r="J57" s="501"/>
-      <c r="K57" s="501"/>
+      <c r="B57" s="502"/>
+      <c r="C57" s="502"/>
+      <c r="D57" s="502"/>
+      <c r="E57" s="502"/>
+      <c r="F57" s="502"/>
+      <c r="G57" s="502"/>
+      <c r="H57" s="502"/>
+      <c r="I57" s="502"/>
+      <c r="J57" s="502"/>
+      <c r="K57" s="502"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="501"/>
-      <c r="B58" s="501"/>
-      <c r="C58" s="501"/>
-      <c r="D58" s="501"/>
-      <c r="E58" s="501"/>
-      <c r="F58" s="501"/>
-      <c r="G58" s="501"/>
-      <c r="H58" s="501"/>
-      <c r="I58" s="501"/>
-      <c r="J58" s="501"/>
-      <c r="K58" s="501"/>
+      <c r="A58" s="502"/>
+      <c r="B58" s="502"/>
+      <c r="C58" s="502"/>
+      <c r="D58" s="502"/>
+      <c r="E58" s="502"/>
+      <c r="F58" s="502"/>
+      <c r="G58" s="502"/>
+      <c r="H58" s="502"/>
+      <c r="I58" s="502"/>
+      <c r="J58" s="502"/>
+      <c r="K58" s="502"/>
     </row>
     <row r="59" spans="1:12" ht="6.95" customHeight="1">
-      <c r="A59" s="501"/>
-      <c r="B59" s="501"/>
-      <c r="C59" s="501"/>
-      <c r="D59" s="501"/>
-      <c r="E59" s="501"/>
-      <c r="F59" s="501"/>
-      <c r="G59" s="501"/>
-      <c r="H59" s="501"/>
-      <c r="I59" s="501"/>
-      <c r="J59" s="501"/>
-      <c r="K59" s="501"/>
+      <c r="A59" s="502"/>
+      <c r="B59" s="502"/>
+      <c r="C59" s="502"/>
+      <c r="D59" s="502"/>
+      <c r="E59" s="502"/>
+      <c r="F59" s="502"/>
+      <c r="G59" s="502"/>
+      <c r="H59" s="502"/>
+      <c r="I59" s="502"/>
+      <c r="J59" s="502"/>
+      <c r="K59" s="502"/>
     </row>
     <row r="60" spans="1:12" ht="8.1" customHeight="1">
-      <c r="A60" s="501"/>
-      <c r="B60" s="501"/>
-      <c r="C60" s="501"/>
-      <c r="D60" s="501"/>
-      <c r="E60" s="501"/>
-      <c r="F60" s="501"/>
-      <c r="G60" s="501"/>
-      <c r="H60" s="501"/>
-      <c r="I60" s="501"/>
-      <c r="J60" s="501"/>
-      <c r="K60" s="501"/>
+      <c r="A60" s="502"/>
+      <c r="B60" s="502"/>
+      <c r="C60" s="502"/>
+      <c r="D60" s="502"/>
+      <c r="E60" s="502"/>
+      <c r="F60" s="502"/>
+      <c r="G60" s="502"/>
+      <c r="H60" s="502"/>
+      <c r="I60" s="502"/>
+      <c r="J60" s="502"/>
+      <c r="K60" s="502"/>
     </row>
     <row r="61" spans="1:12" ht="6.95" customHeight="1">
-      <c r="A61" s="501"/>
-      <c r="B61" s="501"/>
-      <c r="C61" s="501"/>
-      <c r="D61" s="501"/>
-      <c r="E61" s="501"/>
-      <c r="F61" s="501"/>
-      <c r="G61" s="501"/>
-      <c r="H61" s="501"/>
-      <c r="I61" s="501"/>
-      <c r="J61" s="501"/>
-      <c r="K61" s="501"/>
+      <c r="A61" s="502"/>
+      <c r="B61" s="502"/>
+      <c r="C61" s="502"/>
+      <c r="D61" s="502"/>
+      <c r="E61" s="502"/>
+      <c r="F61" s="502"/>
+      <c r="G61" s="502"/>
+      <c r="H61" s="502"/>
+      <c r="I61" s="502"/>
+      <c r="J61" s="502"/>
+      <c r="K61" s="502"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8505,29 +8505,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12">
-      <c r="K2" s="492" t="s">
+      <c r="K2" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="L2" s="492"/>
+      <c r="L2" s="493"/>
     </row>
     <row r="3" spans="2:12" ht="21.75" thickBot="1">
       <c r="B3" s="144" t="s">
         <v>416</v>
       </c>
-      <c r="K3" s="493"/>
-      <c r="L3" s="493"/>
+      <c r="K3" s="494"/>
+      <c r="L3" s="494"/>
     </row>
     <row r="4" spans="2:12" ht="33.75">
-      <c r="B4" s="504" t="s">
+      <c r="B4" s="508" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="505"/>
-      <c r="D4" s="505"/>
-      <c r="E4" s="505"/>
-      <c r="F4" s="505"/>
-      <c r="G4" s="505"/>
-      <c r="H4" s="505"/>
-      <c r="I4" s="506"/>
+      <c r="C4" s="509"/>
+      <c r="D4" s="509"/>
+      <c r="E4" s="509"/>
+      <c r="F4" s="509"/>
+      <c r="G4" s="509"/>
+      <c r="H4" s="509"/>
+      <c r="I4" s="510"/>
     </row>
     <row r="5" spans="2:12" ht="16.5" thickBot="1">
       <c r="B5" s="145" t="s">
@@ -8548,10 +8548,10 @@
       <c r="G5" s="146" t="s">
         <v>200</v>
       </c>
-      <c r="H5" s="507" t="s">
+      <c r="H5" s="511" t="s">
         <v>201</v>
       </c>
-      <c r="I5" s="508"/>
+      <c r="I5" s="512"/>
     </row>
     <row r="6" spans="2:12" ht="16.5" thickBot="1">
       <c r="B6" s="147"/>
@@ -8629,10 +8629,10 @@
       <c r="G9" s="150" t="s">
         <v>200</v>
       </c>
-      <c r="H9" s="509" t="s">
+      <c r="H9" s="513" t="s">
         <v>212</v>
       </c>
-      <c r="I9" s="510"/>
+      <c r="I9" s="514"/>
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="151" t="s">
@@ -8656,11 +8656,11 @@
         <f>F10/C6</f>
         <v>160</v>
       </c>
-      <c r="H10" s="511">
+      <c r="H10" s="505">
         <f>G10/$I$7</f>
         <v>290.90909090909088</v>
       </c>
-      <c r="I10" s="512"/>
+      <c r="I10" s="506"/>
     </row>
     <row r="11" spans="2:12" ht="17.25">
       <c r="B11" s="157" t="s">
@@ -8684,11 +8684,11 @@
         <f>F11/20</f>
         <v>0</v>
       </c>
-      <c r="H11" s="513">
+      <c r="H11" s="515">
         <f>G11/$I$7</f>
         <v>0</v>
       </c>
-      <c r="I11" s="514"/>
+      <c r="I11" s="516"/>
     </row>
     <row r="12" spans="2:12" ht="17.25">
       <c r="B12" s="151" t="s">
@@ -8755,11 +8755,11 @@
         <f>F15/20</f>
         <v>25</v>
       </c>
-      <c r="H15" s="502">
+      <c r="H15" s="503">
         <f>G15/$I$8</f>
         <v>3.787878787878788E-2</v>
       </c>
-      <c r="I15" s="503"/>
+      <c r="I15" s="504"/>
     </row>
     <row r="16" spans="2:12">
       <c r="B16" s="147" t="s">
@@ -8783,11 +8783,11 @@
         <f>F16/20</f>
         <v>15</v>
       </c>
-      <c r="H16" s="502">
+      <c r="H16" s="503">
         <f t="shared" ref="H16:H31" si="0">G16/$I$8</f>
         <v>2.2727272727272728E-2</v>
       </c>
-      <c r="I16" s="503"/>
+      <c r="I16" s="504"/>
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="147" t="s">
@@ -8811,11 +8811,11 @@
         <f>F17/20</f>
         <v>27.5</v>
       </c>
-      <c r="H17" s="502">
+      <c r="H17" s="503">
         <f t="shared" si="0"/>
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="I17" s="503"/>
+      <c r="I17" s="504"/>
     </row>
     <row r="18" spans="2:10">
       <c r="B18" s="147" t="s">
@@ -8839,11 +8839,11 @@
       <c r="G18" s="422">
         <v>1.25</v>
       </c>
-      <c r="H18" s="502">
+      <c r="H18" s="503">
         <f t="shared" si="0"/>
         <v>1.893939393939394E-3</v>
       </c>
-      <c r="I18" s="503"/>
+      <c r="I18" s="504"/>
     </row>
     <row r="19" spans="2:10">
       <c r="B19" s="147" t="s">
@@ -8866,11 +8866,11 @@
       <c r="G19" s="422">
         <v>1</v>
       </c>
-      <c r="H19" s="502">
+      <c r="H19" s="503">
         <f t="shared" si="0"/>
         <v>1.5151515151515152E-3</v>
       </c>
-      <c r="I19" s="503"/>
+      <c r="I19" s="504"/>
     </row>
     <row r="20" spans="2:10">
       <c r="B20" s="147" t="s">
@@ -8894,11 +8894,11 @@
         <f>F20/20</f>
         <v>100</v>
       </c>
-      <c r="H20" s="502">
+      <c r="H20" s="503">
         <f t="shared" si="0"/>
         <v>0.15151515151515152</v>
       </c>
-      <c r="I20" s="503"/>
+      <c r="I20" s="504"/>
     </row>
     <row r="21" spans="2:10">
       <c r="B21" s="147" t="s">
@@ -8922,11 +8922,11 @@
         <f>F21/20</f>
         <v>1452.0000000000002</v>
       </c>
-      <c r="H21" s="502">
+      <c r="H21" s="503">
         <f t="shared" si="0"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="I21" s="503"/>
+      <c r="I21" s="504"/>
     </row>
     <row r="22" spans="2:10">
       <c r="B22" s="147" t="s">
@@ -8950,11 +8950,11 @@
         <f>F22/20</f>
         <v>35</v>
       </c>
-      <c r="H22" s="502">
+      <c r="H22" s="503">
         <f t="shared" si="0"/>
         <v>5.3030303030303032E-2</v>
       </c>
-      <c r="I22" s="503"/>
+      <c r="I22" s="504"/>
     </row>
     <row r="23" spans="2:10">
       <c r="B23" s="147" t="s">
@@ -8977,11 +8977,11 @@
       <c r="G23" s="422">
         <v>24</v>
       </c>
-      <c r="H23" s="502">
+      <c r="H23" s="503">
         <f t="shared" si="0"/>
         <v>3.6363636363636362E-2</v>
       </c>
-      <c r="I23" s="503"/>
+      <c r="I23" s="504"/>
     </row>
     <row r="24" spans="2:10">
       <c r="B24" s="147" t="s">
@@ -9004,11 +9004,11 @@
       <c r="G24" s="422">
         <v>185.40983606557376</v>
       </c>
-      <c r="H24" s="502">
+      <c r="H24" s="503">
         <f t="shared" si="0"/>
         <v>0.28092399403874813</v>
       </c>
-      <c r="I24" s="503"/>
+      <c r="I24" s="504"/>
     </row>
     <row r="25" spans="2:10">
       <c r="B25" s="147" t="s">
@@ -9031,11 +9031,11 @@
       <c r="G25" s="422">
         <v>13.65</v>
       </c>
-      <c r="H25" s="502">
+      <c r="H25" s="503">
         <f t="shared" si="0"/>
         <v>2.0681818181818183E-2</v>
       </c>
-      <c r="I25" s="503"/>
+      <c r="I25" s="504"/>
     </row>
     <row r="26" spans="2:10">
       <c r="B26" s="170" t="s">
@@ -9052,11 +9052,11 @@
         <f>SUM(G10:G25)</f>
         <v>2039.809836065574</v>
       </c>
-      <c r="H26" s="502">
+      <c r="H26" s="503">
         <f t="shared" si="0"/>
         <v>3.0906209637357183</v>
       </c>
-      <c r="I26" s="503"/>
+      <c r="I26" s="504"/>
     </row>
     <row r="27" spans="2:10">
       <c r="B27" s="172" t="s">
@@ -9064,11 +9064,11 @@
       </c>
       <c r="F27" s="422"/>
       <c r="G27" s="426"/>
-      <c r="H27" s="502">
+      <c r="H27" s="503">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="503"/>
+      <c r="I27" s="504"/>
     </row>
     <row r="28" spans="2:10">
       <c r="B28" s="147" t="s">
@@ -9081,11 +9081,11 @@
         <f>F28/20</f>
         <v>60</v>
       </c>
-      <c r="H28" s="502">
+      <c r="H28" s="503">
         <f t="shared" si="0"/>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="I28" s="503"/>
+      <c r="I28" s="504"/>
     </row>
     <row r="29" spans="2:10">
       <c r="B29" s="147" t="s">
@@ -9098,11 +9098,11 @@
         <f>F29/20</f>
         <v>22</v>
       </c>
-      <c r="H29" s="502">
+      <c r="H29" s="503">
         <f t="shared" si="0"/>
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="I29" s="503"/>
+      <c r="I29" s="504"/>
     </row>
     <row r="30" spans="2:10">
       <c r="B30" s="172" t="s">
@@ -9116,11 +9116,11 @@
         <f>G28+G29</f>
         <v>82</v>
       </c>
-      <c r="H30" s="502">
+      <c r="H30" s="503">
         <f t="shared" si="0"/>
         <v>0.12424242424242424</v>
       </c>
-      <c r="I30" s="503"/>
+      <c r="I30" s="504"/>
     </row>
     <row r="31" spans="2:10" ht="16.5" thickBot="1">
       <c r="B31" s="432" t="s">
@@ -9137,11 +9137,11 @@
         <f>G26+G6+G30</f>
         <v>3496.809836065574</v>
       </c>
-      <c r="H31" s="511">
+      <c r="H31" s="505">
         <f t="shared" si="0"/>
         <v>5.2981967213114753</v>
       </c>
-      <c r="I31" s="512"/>
+      <c r="I31" s="506"/>
       <c r="J31" t="s">
         <v>242</v>
       </c>
@@ -9183,11 +9183,11 @@
       <c r="I33" s="168"/>
     </row>
     <row r="34" spans="1:12" ht="17.25">
-      <c r="B34" s="515" t="s">
+      <c r="B34" s="507" t="s">
         <v>245</v>
       </c>
-      <c r="C34" s="515"/>
-      <c r="D34" s="515"/>
+      <c r="C34" s="507"/>
+      <c r="D34" s="507"/>
       <c r="L34">
         <f>50/H38</f>
         <v>2.1917808219178081</v>
@@ -9224,11 +9224,13 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="K2:L3"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
     <mergeCell ref="H27:I27"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="H17:I17"/>
@@ -9241,13 +9243,11 @@
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="H25:I25"/>
     <mergeCell ref="H26:I26"/>
-    <mergeCell ref="K2:L3"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L8" r:id="rId1" xr:uid="{F7409163-740C-D24A-84CB-4E3439D40069}"/>
@@ -9270,29 +9270,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12">
-      <c r="K2" s="492" t="s">
+      <c r="K2" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="L2" s="492"/>
+      <c r="L2" s="493"/>
     </row>
     <row r="3" spans="2:12" ht="21.75" thickBot="1">
       <c r="B3" s="144" t="s">
         <v>247</v>
       </c>
-      <c r="K3" s="493"/>
-      <c r="L3" s="493"/>
+      <c r="K3" s="494"/>
+      <c r="L3" s="494"/>
     </row>
     <row r="4" spans="2:12" ht="33.75">
-      <c r="B4" s="504" t="s">
+      <c r="B4" s="508" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="505"/>
-      <c r="D4" s="505"/>
-      <c r="E4" s="505"/>
-      <c r="F4" s="505"/>
-      <c r="G4" s="505"/>
-      <c r="H4" s="505"/>
-      <c r="I4" s="506"/>
+      <c r="C4" s="509"/>
+      <c r="D4" s="509"/>
+      <c r="E4" s="509"/>
+      <c r="F4" s="509"/>
+      <c r="G4" s="509"/>
+      <c r="H4" s="509"/>
+      <c r="I4" s="510"/>
     </row>
     <row r="5" spans="2:12" ht="16.5" thickBot="1">
       <c r="B5" s="145" t="s">
@@ -9313,10 +9313,10 @@
       <c r="G5" s="146" t="s">
         <v>200</v>
       </c>
-      <c r="H5" s="507" t="s">
+      <c r="H5" s="511" t="s">
         <v>201</v>
       </c>
-      <c r="I5" s="508"/>
+      <c r="I5" s="512"/>
     </row>
     <row r="6" spans="2:12" ht="16.5" thickBot="1">
       <c r="B6" s="147"/>
@@ -9394,10 +9394,10 @@
       <c r="G9" s="150" t="s">
         <v>200</v>
       </c>
-      <c r="H9" s="509" t="s">
+      <c r="H9" s="513" t="s">
         <v>212</v>
       </c>
-      <c r="I9" s="510"/>
+      <c r="I9" s="514"/>
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="151" t="s">
@@ -9421,11 +9421,11 @@
         <f>F10/C6</f>
         <v>160</v>
       </c>
-      <c r="H10" s="511" t="e">
+      <c r="H10" s="505" t="e">
         <f>G10/$J$7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I10" s="512"/>
+      <c r="I10" s="506"/>
     </row>
     <row r="11" spans="2:12" ht="17.25">
       <c r="B11" s="157" t="s">
@@ -9449,11 +9449,11 @@
         <f>F11/20</f>
         <v>0</v>
       </c>
-      <c r="H11" s="513" t="e">
+      <c r="H11" s="515" t="e">
         <f t="shared" ref="H11" si="0">G11/$J$7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I11" s="514"/>
+      <c r="I11" s="516"/>
     </row>
     <row r="12" spans="2:12" ht="17.25">
       <c r="B12" s="151" t="s">
@@ -9520,11 +9520,11 @@
         <f>F15/C6</f>
         <v>25</v>
       </c>
-      <c r="H15" s="502">
+      <c r="H15" s="503">
         <f>G15/$I$8</f>
         <v>3.787878787878788E-2</v>
       </c>
-      <c r="I15" s="503"/>
+      <c r="I15" s="504"/>
     </row>
     <row r="16" spans="2:12">
       <c r="B16" s="147" t="s">
@@ -9548,11 +9548,11 @@
         <f>F16/C6</f>
         <v>15</v>
       </c>
-      <c r="H16" s="502">
+      <c r="H16" s="503">
         <f t="shared" ref="H16:H32" si="1">G16/$I$8</f>
         <v>2.2727272727272728E-2</v>
       </c>
-      <c r="I16" s="503"/>
+      <c r="I16" s="504"/>
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="147" t="s">
@@ -9576,11 +9576,11 @@
         <f>F17/C6</f>
         <v>27.5</v>
       </c>
-      <c r="H17" s="502">
+      <c r="H17" s="503">
         <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="I17" s="503"/>
+      <c r="I17" s="504"/>
     </row>
     <row r="18" spans="2:10">
       <c r="B18" s="147" t="s">
@@ -9604,11 +9604,11 @@
       <c r="G18" s="422">
         <v>1.25</v>
       </c>
-      <c r="H18" s="502">
+      <c r="H18" s="503">
         <f t="shared" si="1"/>
         <v>1.893939393939394E-3</v>
       </c>
-      <c r="I18" s="503"/>
+      <c r="I18" s="504"/>
     </row>
     <row r="19" spans="2:10">
       <c r="B19" s="147" t="s">
@@ -9632,11 +9632,11 @@
         <f>D19</f>
         <v>60</v>
       </c>
-      <c r="H19" s="502">
+      <c r="H19" s="503">
         <f t="shared" ref="H19" si="2">G19/$I$8</f>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="I19" s="503"/>
+      <c r="I19" s="504"/>
     </row>
     <row r="20" spans="2:10">
       <c r="B20" s="147"/>
@@ -9657,11 +9657,11 @@
       <c r="G20" s="422">
         <v>1</v>
       </c>
-      <c r="H20" s="502">
+      <c r="H20" s="503">
         <f t="shared" si="1"/>
         <v>1.5151515151515152E-3</v>
       </c>
-      <c r="I20" s="503"/>
+      <c r="I20" s="504"/>
     </row>
     <row r="21" spans="2:10">
       <c r="B21" s="147" t="s">
@@ -9685,11 +9685,11 @@
         <f>F21/20</f>
         <v>100</v>
       </c>
-      <c r="H21" s="502">
+      <c r="H21" s="503">
         <f t="shared" si="1"/>
         <v>0.15151515151515152</v>
       </c>
-      <c r="I21" s="503"/>
+      <c r="I21" s="504"/>
     </row>
     <row r="22" spans="2:10">
       <c r="B22" s="147" t="s">
@@ -9713,11 +9713,11 @@
         <f>F22/20</f>
         <v>1452.0000000000002</v>
       </c>
-      <c r="H22" s="502">
+      <c r="H22" s="503">
         <f t="shared" si="1"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="I22" s="503"/>
+      <c r="I22" s="504"/>
     </row>
     <row r="23" spans="2:10">
       <c r="B23" s="147" t="s">
@@ -9741,11 +9741,11 @@
         <f>F23/20</f>
         <v>35</v>
       </c>
-      <c r="H23" s="502">
+      <c r="H23" s="503">
         <f t="shared" si="1"/>
         <v>5.3030303030303032E-2</v>
       </c>
-      <c r="I23" s="503"/>
+      <c r="I23" s="504"/>
     </row>
     <row r="24" spans="2:10">
       <c r="B24" s="147" t="s">
@@ -9768,11 +9768,11 @@
       <c r="G24" s="422">
         <v>24</v>
       </c>
-      <c r="H24" s="502">
+      <c r="H24" s="503">
         <f t="shared" si="1"/>
         <v>3.6363636363636362E-2</v>
       </c>
-      <c r="I24" s="503"/>
+      <c r="I24" s="504"/>
     </row>
     <row r="25" spans="2:10">
       <c r="B25" s="147" t="s">
@@ -9795,11 +9795,11 @@
       <c r="G25" s="422">
         <v>185.40983606557376</v>
       </c>
-      <c r="H25" s="502">
+      <c r="H25" s="503">
         <f t="shared" si="1"/>
         <v>0.28092399403874813</v>
       </c>
-      <c r="I25" s="503"/>
+      <c r="I25" s="504"/>
     </row>
     <row r="26" spans="2:10">
       <c r="B26" s="147" t="s">
@@ -9822,11 +9822,11 @@
       <c r="G26" s="422">
         <v>13.65</v>
       </c>
-      <c r="H26" s="502">
+      <c r="H26" s="503">
         <f t="shared" si="1"/>
         <v>2.0681818181818183E-2</v>
       </c>
-      <c r="I26" s="503"/>
+      <c r="I26" s="504"/>
     </row>
     <row r="27" spans="2:10">
       <c r="B27" s="170" t="s">
@@ -9843,11 +9843,11 @@
         <f>SUM(G10:G26)</f>
         <v>2099.809836065574</v>
       </c>
-      <c r="H27" s="502">
+      <c r="H27" s="503">
         <f t="shared" si="1"/>
         <v>3.1815300546448091</v>
       </c>
-      <c r="I27" s="503"/>
+      <c r="I27" s="504"/>
     </row>
     <row r="28" spans="2:10">
       <c r="B28" s="172" t="s">
@@ -9855,11 +9855,11 @@
       </c>
       <c r="F28" s="422"/>
       <c r="G28" s="426"/>
-      <c r="H28" s="502">
+      <c r="H28" s="503">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="503"/>
+      <c r="I28" s="504"/>
     </row>
     <row r="29" spans="2:10">
       <c r="B29" s="147" t="s">
@@ -9872,11 +9872,11 @@
         <f>F29/20</f>
         <v>60</v>
       </c>
-      <c r="H29" s="502">
+      <c r="H29" s="503">
         <f t="shared" si="1"/>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="I29" s="503"/>
+      <c r="I29" s="504"/>
     </row>
     <row r="30" spans="2:10">
       <c r="B30" s="147" t="s">
@@ -9889,11 +9889,11 @@
         <f>F30/20</f>
         <v>22</v>
       </c>
-      <c r="H30" s="502">
+      <c r="H30" s="503">
         <f t="shared" si="1"/>
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="I30" s="503"/>
+      <c r="I30" s="504"/>
     </row>
     <row r="31" spans="2:10">
       <c r="B31" s="172" t="s">
@@ -9907,11 +9907,11 @@
         <f>G29+G30</f>
         <v>82</v>
       </c>
-      <c r="H31" s="502">
+      <c r="H31" s="503">
         <f t="shared" si="1"/>
         <v>0.12424242424242424</v>
       </c>
-      <c r="I31" s="503"/>
+      <c r="I31" s="504"/>
     </row>
     <row r="32" spans="2:10" ht="16.5" thickBot="1">
       <c r="B32" s="432" t="s">
@@ -9928,11 +9928,11 @@
         <f>G27+G6+G31</f>
         <v>3556.809836065574</v>
       </c>
-      <c r="H32" s="511">
+      <c r="H32" s="505">
         <f t="shared" si="1"/>
         <v>5.3891058122205671</v>
       </c>
-      <c r="I32" s="512"/>
+      <c r="I32" s="506"/>
       <c r="J32" t="s">
         <v>242</v>
       </c>
@@ -9974,11 +9974,11 @@
       <c r="I34" s="168"/>
     </row>
     <row r="35" spans="1:9" ht="17.25">
-      <c r="B35" s="515" t="s">
+      <c r="B35" s="507" t="s">
         <v>245</v>
       </c>
-      <c r="C35" s="515"/>
-      <c r="D35" s="515"/>
+      <c r="C35" s="507"/>
+      <c r="D35" s="507"/>
     </row>
     <row r="36" spans="1:9" ht="17.25">
       <c r="B36" s="174" t="s">
@@ -9999,16 +9999,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
     <mergeCell ref="K2:L3"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="H28:I28"/>
@@ -10024,6 +10014,16 @@
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L8" r:id="rId1" xr:uid="{C10CBC37-B907-284D-A5CD-D379AFEFC3CE}"/>
@@ -10043,17 +10043,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="16.5" thickBot="1">
-      <c r="O2" s="492" t="s">
+      <c r="O2" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="P2" s="492"/>
+      <c r="P2" s="493"/>
     </row>
     <row r="3" spans="1:16" ht="16.5" thickBot="1">
       <c r="C3" s="178" t="s">
         <v>253</v>
       </c>
-      <c r="O3" s="493"/>
-      <c r="P3" s="493"/>
+      <c r="O3" s="494"/>
+      <c r="P3" s="494"/>
     </row>
     <row r="4" spans="1:16" ht="24" thickBot="1">
       <c r="B4" s="179" t="s">
@@ -10072,10 +10072,10 @@
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="C6" s="517" t="s">
+      <c r="C6" s="518" t="s">
         <v>256</v>
       </c>
-      <c r="D6" s="517"/>
+      <c r="D6" s="518"/>
       <c r="H6" t="s">
         <v>257</v>
       </c>
@@ -10644,36 +10644,36 @@
       </c>
     </row>
     <row r="31" spans="1:15">
-      <c r="C31" s="516" t="s">
+      <c r="C31" s="517" t="s">
         <v>293</v>
       </c>
-      <c r="D31" s="516"/>
-      <c r="E31" s="516"/>
-      <c r="F31" s="516"/>
-      <c r="G31" s="516"/>
-      <c r="H31" s="516"/>
-      <c r="I31" s="516"/>
-      <c r="J31" s="516"/>
-      <c r="K31" s="516"/>
-      <c r="L31" s="516"/>
-      <c r="M31" s="516"/>
-      <c r="N31" s="516"/>
-      <c r="O31" s="516"/>
+      <c r="D31" s="517"/>
+      <c r="E31" s="517"/>
+      <c r="F31" s="517"/>
+      <c r="G31" s="517"/>
+      <c r="H31" s="517"/>
+      <c r="I31" s="517"/>
+      <c r="J31" s="517"/>
+      <c r="K31" s="517"/>
+      <c r="L31" s="517"/>
+      <c r="M31" s="517"/>
+      <c r="N31" s="517"/>
+      <c r="O31" s="517"/>
     </row>
     <row r="32" spans="1:15">
-      <c r="C32" s="516"/>
-      <c r="D32" s="516"/>
-      <c r="E32" s="516"/>
-      <c r="F32" s="516"/>
-      <c r="G32" s="516"/>
-      <c r="H32" s="516"/>
-      <c r="I32" s="516"/>
-      <c r="J32" s="516"/>
-      <c r="K32" s="516"/>
-      <c r="L32" s="516"/>
-      <c r="M32" s="516"/>
-      <c r="N32" s="516"/>
-      <c r="O32" s="516"/>
+      <c r="C32" s="517"/>
+      <c r="D32" s="517"/>
+      <c r="E32" s="517"/>
+      <c r="F32" s="517"/>
+      <c r="G32" s="517"/>
+      <c r="H32" s="517"/>
+      <c r="I32" s="517"/>
+      <c r="J32" s="517"/>
+      <c r="K32" s="517"/>
+      <c r="L32" s="517"/>
+      <c r="M32" s="517"/>
+      <c r="N32" s="517"/>
+      <c r="O32" s="517"/>
     </row>
     <row r="33" spans="3:18">
       <c r="C33" t="s">
@@ -10681,151 +10681,151 @@
       </c>
     </row>
     <row r="34" spans="3:18">
-      <c r="C34" s="516" t="s">
+      <c r="C34" s="517" t="s">
         <v>294</v>
       </c>
-      <c r="D34" s="516"/>
-      <c r="E34" s="516"/>
-      <c r="F34" s="516"/>
-      <c r="G34" s="516"/>
-      <c r="H34" s="516"/>
-      <c r="I34" s="516"/>
-      <c r="J34" s="516"/>
-      <c r="K34" s="516"/>
-      <c r="L34" s="516"/>
-      <c r="M34" s="516"/>
-      <c r="N34" s="516"/>
-      <c r="O34" s="516"/>
-      <c r="P34" s="516"/>
-      <c r="Q34" s="516"/>
-      <c r="R34" s="516"/>
+      <c r="D34" s="517"/>
+      <c r="E34" s="517"/>
+      <c r="F34" s="517"/>
+      <c r="G34" s="517"/>
+      <c r="H34" s="517"/>
+      <c r="I34" s="517"/>
+      <c r="J34" s="517"/>
+      <c r="K34" s="517"/>
+      <c r="L34" s="517"/>
+      <c r="M34" s="517"/>
+      <c r="N34" s="517"/>
+      <c r="O34" s="517"/>
+      <c r="P34" s="517"/>
+      <c r="Q34" s="517"/>
+      <c r="R34" s="517"/>
     </row>
     <row r="35" spans="3:18">
-      <c r="C35" s="516"/>
-      <c r="D35" s="516"/>
-      <c r="E35" s="516"/>
-      <c r="F35" s="516"/>
-      <c r="G35" s="516"/>
-      <c r="H35" s="516"/>
-      <c r="I35" s="516"/>
-      <c r="J35" s="516"/>
-      <c r="K35" s="516"/>
-      <c r="L35" s="516"/>
-      <c r="M35" s="516"/>
-      <c r="N35" s="516"/>
-      <c r="O35" s="516"/>
-      <c r="P35" s="516"/>
-      <c r="Q35" s="516"/>
-      <c r="R35" s="516"/>
+      <c r="C35" s="517"/>
+      <c r="D35" s="517"/>
+      <c r="E35" s="517"/>
+      <c r="F35" s="517"/>
+      <c r="G35" s="517"/>
+      <c r="H35" s="517"/>
+      <c r="I35" s="517"/>
+      <c r="J35" s="517"/>
+      <c r="K35" s="517"/>
+      <c r="L35" s="517"/>
+      <c r="M35" s="517"/>
+      <c r="N35" s="517"/>
+      <c r="O35" s="517"/>
+      <c r="P35" s="517"/>
+      <c r="Q35" s="517"/>
+      <c r="R35" s="517"/>
     </row>
     <row r="36" spans="3:18">
-      <c r="C36" s="516" t="s">
+      <c r="C36" s="517" t="s">
         <v>295</v>
       </c>
-      <c r="D36" s="516"/>
-      <c r="E36" s="516"/>
-      <c r="F36" s="516"/>
-      <c r="G36" s="516"/>
-      <c r="H36" s="516"/>
-      <c r="I36" s="516"/>
-      <c r="J36" s="516"/>
-      <c r="K36" s="516"/>
-      <c r="L36" s="516"/>
-      <c r="M36" s="516"/>
-      <c r="N36" s="516"/>
-      <c r="O36" s="516"/>
+      <c r="D36" s="517"/>
+      <c r="E36" s="517"/>
+      <c r="F36" s="517"/>
+      <c r="G36" s="517"/>
+      <c r="H36" s="517"/>
+      <c r="I36" s="517"/>
+      <c r="J36" s="517"/>
+      <c r="K36" s="517"/>
+      <c r="L36" s="517"/>
+      <c r="M36" s="517"/>
+      <c r="N36" s="517"/>
+      <c r="O36" s="517"/>
     </row>
     <row r="37" spans="3:18">
-      <c r="C37" s="516"/>
-      <c r="D37" s="516"/>
-      <c r="E37" s="516"/>
-      <c r="F37" s="516"/>
-      <c r="G37" s="516"/>
-      <c r="H37" s="516"/>
-      <c r="I37" s="516"/>
-      <c r="J37" s="516"/>
-      <c r="K37" s="516"/>
-      <c r="L37" s="516"/>
-      <c r="M37" s="516"/>
-      <c r="N37" s="516"/>
-      <c r="O37" s="516"/>
+      <c r="C37" s="517"/>
+      <c r="D37" s="517"/>
+      <c r="E37" s="517"/>
+      <c r="F37" s="517"/>
+      <c r="G37" s="517"/>
+      <c r="H37" s="517"/>
+      <c r="I37" s="517"/>
+      <c r="J37" s="517"/>
+      <c r="K37" s="517"/>
+      <c r="L37" s="517"/>
+      <c r="M37" s="517"/>
+      <c r="N37" s="517"/>
+      <c r="O37" s="517"/>
     </row>
     <row r="38" spans="3:18">
-      <c r="C38" s="516" t="s">
+      <c r="C38" s="517" t="s">
         <v>296</v>
       </c>
-      <c r="D38" s="516"/>
-      <c r="E38" s="516"/>
-      <c r="F38" s="516"/>
-      <c r="G38" s="516"/>
-      <c r="H38" s="516"/>
-      <c r="I38" s="516"/>
-      <c r="J38" s="516"/>
-      <c r="K38" s="516"/>
-      <c r="L38" s="516"/>
-      <c r="M38" s="516"/>
-      <c r="N38" s="516"/>
-      <c r="O38" s="516"/>
+      <c r="D38" s="517"/>
+      <c r="E38" s="517"/>
+      <c r="F38" s="517"/>
+      <c r="G38" s="517"/>
+      <c r="H38" s="517"/>
+      <c r="I38" s="517"/>
+      <c r="J38" s="517"/>
+      <c r="K38" s="517"/>
+      <c r="L38" s="517"/>
+      <c r="M38" s="517"/>
+      <c r="N38" s="517"/>
+      <c r="O38" s="517"/>
     </row>
     <row r="39" spans="3:18">
-      <c r="C39" s="516"/>
-      <c r="D39" s="516"/>
-      <c r="E39" s="516"/>
-      <c r="F39" s="516"/>
-      <c r="G39" s="516"/>
-      <c r="H39" s="516"/>
-      <c r="I39" s="516"/>
-      <c r="J39" s="516"/>
-      <c r="K39" s="516"/>
-      <c r="L39" s="516"/>
-      <c r="M39" s="516"/>
-      <c r="N39" s="516"/>
-      <c r="O39" s="516"/>
+      <c r="C39" s="517"/>
+      <c r="D39" s="517"/>
+      <c r="E39" s="517"/>
+      <c r="F39" s="517"/>
+      <c r="G39" s="517"/>
+      <c r="H39" s="517"/>
+      <c r="I39" s="517"/>
+      <c r="J39" s="517"/>
+      <c r="K39" s="517"/>
+      <c r="L39" s="517"/>
+      <c r="M39" s="517"/>
+      <c r="N39" s="517"/>
+      <c r="O39" s="517"/>
     </row>
     <row r="40" spans="3:18">
-      <c r="C40" s="516"/>
-      <c r="D40" s="516"/>
-      <c r="E40" s="516"/>
-      <c r="F40" s="516"/>
-      <c r="G40" s="516"/>
-      <c r="H40" s="516"/>
-      <c r="I40" s="516"/>
-      <c r="J40" s="516"/>
-      <c r="K40" s="516"/>
-      <c r="L40" s="516"/>
-      <c r="M40" s="516"/>
-      <c r="N40" s="516"/>
-      <c r="O40" s="516"/>
+      <c r="C40" s="517"/>
+      <c r="D40" s="517"/>
+      <c r="E40" s="517"/>
+      <c r="F40" s="517"/>
+      <c r="G40" s="517"/>
+      <c r="H40" s="517"/>
+      <c r="I40" s="517"/>
+      <c r="J40" s="517"/>
+      <c r="K40" s="517"/>
+      <c r="L40" s="517"/>
+      <c r="M40" s="517"/>
+      <c r="N40" s="517"/>
+      <c r="O40" s="517"/>
     </row>
     <row r="41" spans="3:18">
-      <c r="C41" s="516"/>
-      <c r="D41" s="516"/>
-      <c r="E41" s="516"/>
-      <c r="F41" s="516"/>
-      <c r="G41" s="516"/>
-      <c r="H41" s="516"/>
-      <c r="I41" s="516"/>
-      <c r="J41" s="516"/>
-      <c r="K41" s="516"/>
-      <c r="L41" s="516"/>
-      <c r="M41" s="516"/>
-      <c r="N41" s="516"/>
-      <c r="O41" s="516"/>
+      <c r="C41" s="517"/>
+      <c r="D41" s="517"/>
+      <c r="E41" s="517"/>
+      <c r="F41" s="517"/>
+      <c r="G41" s="517"/>
+      <c r="H41" s="517"/>
+      <c r="I41" s="517"/>
+      <c r="J41" s="517"/>
+      <c r="K41" s="517"/>
+      <c r="L41" s="517"/>
+      <c r="M41" s="517"/>
+      <c r="N41" s="517"/>
+      <c r="O41" s="517"/>
     </row>
     <row r="42" spans="3:18">
-      <c r="C42" s="516"/>
-      <c r="D42" s="516"/>
-      <c r="E42" s="516"/>
-      <c r="F42" s="516"/>
-      <c r="G42" s="516"/>
-      <c r="H42" s="516"/>
-      <c r="I42" s="516"/>
-      <c r="J42" s="516"/>
-      <c r="K42" s="516"/>
-      <c r="L42" s="516"/>
-      <c r="M42" s="516"/>
-      <c r="N42" s="516"/>
-      <c r="O42" s="516"/>
+      <c r="C42" s="517"/>
+      <c r="D42" s="517"/>
+      <c r="E42" s="517"/>
+      <c r="F42" s="517"/>
+      <c r="G42" s="517"/>
+      <c r="H42" s="517"/>
+      <c r="I42" s="517"/>
+      <c r="J42" s="517"/>
+      <c r="K42" s="517"/>
+      <c r="L42" s="517"/>
+      <c r="M42" s="517"/>
+      <c r="N42" s="517"/>
+      <c r="O42" s="517"/>
     </row>
     <row r="43" spans="3:18">
       <c r="C43" t="s">
@@ -10884,103 +10884,103 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14">
-      <c r="M3" s="492" t="s">
+      <c r="M3" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="N3" s="492"/>
+      <c r="N3" s="493"/>
     </row>
     <row r="4" spans="2:14" ht="26.25">
       <c r="B4" s="338" t="s">
         <v>417</v>
       </c>
-      <c r="M4" s="493"/>
-      <c r="N4" s="493"/>
+      <c r="M4" s="494"/>
+      <c r="N4" s="494"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="516" t="s">
+      <c r="B6" s="517" t="s">
         <v>418</v>
       </c>
-      <c r="C6" s="518"/>
-      <c r="D6" s="518"/>
-      <c r="E6" s="518"/>
-      <c r="F6" s="518"/>
-      <c r="G6" s="518"/>
-      <c r="H6" s="518"/>
-      <c r="I6" s="518"/>
-      <c r="J6" s="518"/>
-      <c r="K6" s="518"/>
+      <c r="C6" s="519"/>
+      <c r="D6" s="519"/>
+      <c r="E6" s="519"/>
+      <c r="F6" s="519"/>
+      <c r="G6" s="519"/>
+      <c r="H6" s="519"/>
+      <c r="I6" s="519"/>
+      <c r="J6" s="519"/>
+      <c r="K6" s="519"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="518"/>
-      <c r="C7" s="518"/>
-      <c r="D7" s="518"/>
-      <c r="E7" s="518"/>
-      <c r="F7" s="518"/>
-      <c r="G7" s="518"/>
-      <c r="H7" s="518"/>
-      <c r="I7" s="518"/>
-      <c r="J7" s="518"/>
-      <c r="K7" s="518"/>
+      <c r="B7" s="519"/>
+      <c r="C7" s="519"/>
+      <c r="D7" s="519"/>
+      <c r="E7" s="519"/>
+      <c r="F7" s="519"/>
+      <c r="G7" s="519"/>
+      <c r="H7" s="519"/>
+      <c r="I7" s="519"/>
+      <c r="J7" s="519"/>
+      <c r="K7" s="519"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="518"/>
-      <c r="C8" s="518"/>
-      <c r="D8" s="518"/>
-      <c r="E8" s="518"/>
-      <c r="F8" s="518"/>
-      <c r="G8" s="518"/>
-      <c r="H8" s="518"/>
-      <c r="I8" s="518"/>
-      <c r="J8" s="518"/>
-      <c r="K8" s="518"/>
+      <c r="B8" s="519"/>
+      <c r="C8" s="519"/>
+      <c r="D8" s="519"/>
+      <c r="E8" s="519"/>
+      <c r="F8" s="519"/>
+      <c r="G8" s="519"/>
+      <c r="H8" s="519"/>
+      <c r="I8" s="519"/>
+      <c r="J8" s="519"/>
+      <c r="K8" s="519"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="518"/>
-      <c r="C9" s="518"/>
-      <c r="D9" s="518"/>
-      <c r="E9" s="518"/>
-      <c r="F9" s="518"/>
-      <c r="G9" s="518"/>
-      <c r="H9" s="518"/>
-      <c r="I9" s="518"/>
-      <c r="J9" s="518"/>
-      <c r="K9" s="518"/>
+      <c r="B9" s="519"/>
+      <c r="C9" s="519"/>
+      <c r="D9" s="519"/>
+      <c r="E9" s="519"/>
+      <c r="F9" s="519"/>
+      <c r="G9" s="519"/>
+      <c r="H9" s="519"/>
+      <c r="I9" s="519"/>
+      <c r="J9" s="519"/>
+      <c r="K9" s="519"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="B10" s="518"/>
-      <c r="C10" s="518"/>
-      <c r="D10" s="518"/>
-      <c r="E10" s="518"/>
-      <c r="F10" s="518"/>
-      <c r="G10" s="518"/>
-      <c r="H10" s="518"/>
-      <c r="I10" s="518"/>
-      <c r="J10" s="518"/>
-      <c r="K10" s="518"/>
+      <c r="B10" s="519"/>
+      <c r="C10" s="519"/>
+      <c r="D10" s="519"/>
+      <c r="E10" s="519"/>
+      <c r="F10" s="519"/>
+      <c r="G10" s="519"/>
+      <c r="H10" s="519"/>
+      <c r="I10" s="519"/>
+      <c r="J10" s="519"/>
+      <c r="K10" s="519"/>
     </row>
     <row r="11" spans="2:14" ht="2.1" customHeight="1">
-      <c r="B11" s="518"/>
-      <c r="C11" s="518"/>
-      <c r="D11" s="518"/>
-      <c r="E11" s="518"/>
-      <c r="F11" s="518"/>
-      <c r="G11" s="518"/>
-      <c r="H11" s="518"/>
-      <c r="I11" s="518"/>
-      <c r="J11" s="518"/>
-      <c r="K11" s="518"/>
+      <c r="B11" s="519"/>
+      <c r="C11" s="519"/>
+      <c r="D11" s="519"/>
+      <c r="E11" s="519"/>
+      <c r="F11" s="519"/>
+      <c r="G11" s="519"/>
+      <c r="H11" s="519"/>
+      <c r="I11" s="519"/>
+      <c r="J11" s="519"/>
+      <c r="K11" s="519"/>
     </row>
     <row r="12" spans="2:14" hidden="1">
-      <c r="B12" s="518"/>
-      <c r="C12" s="518"/>
-      <c r="D12" s="518"/>
-      <c r="E12" s="518"/>
-      <c r="F12" s="518"/>
-      <c r="G12" s="518"/>
-      <c r="H12" s="518"/>
-      <c r="I12" s="518"/>
-      <c r="J12" s="518"/>
-      <c r="K12" s="518"/>
+      <c r="B12" s="519"/>
+      <c r="C12" s="519"/>
+      <c r="D12" s="519"/>
+      <c r="E12" s="519"/>
+      <c r="F12" s="519"/>
+      <c r="G12" s="519"/>
+      <c r="H12" s="519"/>
+      <c r="I12" s="519"/>
+      <c r="J12" s="519"/>
+      <c r="K12" s="519"/>
     </row>
     <row r="14" spans="2:14" ht="48" thickBot="1">
       <c r="C14" s="236" t="s">
@@ -11082,14 +11082,14 @@
       <c r="B2" s="480" t="s">
         <v>252</v>
       </c>
-      <c r="I2" s="492" t="s">
+      <c r="I2" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="J2" s="492"/>
+      <c r="J2" s="493"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="I3" s="493"/>
-      <c r="J3" s="493"/>
+      <c r="I3" s="494"/>
+      <c r="J3" s="494"/>
     </row>
     <row r="4" spans="2:10">
       <c r="B4" s="142" t="s">
@@ -11151,14 +11151,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
-      <c r="I2" s="492" t="s">
+      <c r="I2" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="J2" s="492"/>
+      <c r="J2" s="493"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="I3" s="493"/>
-      <c r="J3" s="493"/>
+      <c r="I3" s="494"/>
+      <c r="J3" s="494"/>
     </row>
     <row r="5" spans="2:10" ht="23.25">
       <c r="B5" s="480" t="s">
@@ -11181,11 +11181,11 @@
       </c>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="519" t="s">
+      <c r="B12" s="520" t="s">
         <v>548</v>
       </c>
-      <c r="C12" s="519"/>
-      <c r="D12" s="519"/>
+      <c r="C12" s="520"/>
+      <c r="D12" s="520"/>
     </row>
     <row r="13" spans="2:10" ht="33.950000000000003" customHeight="1">
       <c r="B13" s="198" t="s">
@@ -11462,14 +11462,14 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14">
-      <c r="M3" s="492" t="s">
+      <c r="M3" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="N3" s="492"/>
+      <c r="N3" s="493"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="M4" s="493"/>
-      <c r="N4" s="493"/>
+      <c r="M4" s="494"/>
+      <c r="N4" s="494"/>
     </row>
     <row r="5" spans="2:14" ht="23.25">
       <c r="B5" s="480" t="s">
@@ -11492,11 +11492,11 @@
       </c>
     </row>
     <row r="12" spans="2:14">
-      <c r="B12" s="519" t="s">
+      <c r="B12" s="520" t="s">
         <v>548</v>
       </c>
-      <c r="C12" s="519"/>
-      <c r="D12" s="519"/>
+      <c r="C12" s="520"/>
+      <c r="D12" s="520"/>
     </row>
     <row r="13" spans="2:14">
       <c r="B13" s="198" t="s">
@@ -11772,14 +11772,14 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="2" spans="15:16">
-      <c r="O2" s="492" t="s">
+      <c r="O2" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="P2" s="492"/>
+      <c r="P2" s="493"/>
     </row>
     <row r="3" spans="15:16">
-      <c r="O3" s="493"/>
-      <c r="P3" s="493"/>
+      <c r="O3" s="494"/>
+      <c r="P3" s="494"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -14108,10 +14108,10 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="L6" s="492" t="s">
+      <c r="L6" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="M6" s="492"/>
+      <c r="M6" s="493"/>
     </row>
     <row r="7" spans="1:13" ht="24" customHeight="1">
       <c r="A7" s="9" t="s">
@@ -14130,8 +14130,8 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
-      <c r="L7" s="493"/>
-      <c r="M7" s="493"/>
+      <c r="L7" s="494"/>
+      <c r="M7" s="494"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="358" t="s">
@@ -15102,10 +15102,10 @@
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
-      <c r="E53" s="490" t="s">
+      <c r="E53" s="491" t="s">
         <v>471</v>
       </c>
-      <c r="F53" s="490"/>
+      <c r="F53" s="491"/>
       <c r="G53" s="372">
         <v>143</v>
       </c>
@@ -15122,8 +15122,8 @@
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
-      <c r="E54" s="491"/>
-      <c r="F54" s="491"/>
+      <c r="E54" s="492"/>
+      <c r="F54" s="492"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
@@ -15542,18 +15542,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.25">
-      <c r="A1" s="494" t="s">
+      <c r="A1" s="495" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="494"/>
-      <c r="C1" s="494"/>
-      <c r="D1" s="494"/>
-      <c r="E1" s="494"/>
-      <c r="F1" s="494"/>
-      <c r="G1" s="494"/>
-      <c r="H1" s="494"/>
-      <c r="I1" s="494"/>
-      <c r="J1" s="494"/>
+      <c r="B1" s="495"/>
+      <c r="C1" s="495"/>
+      <c r="D1" s="495"/>
+      <c r="E1" s="495"/>
+      <c r="F1" s="495"/>
+      <c r="G1" s="495"/>
+      <c r="H1" s="495"/>
+      <c r="I1" s="495"/>
+      <c r="J1" s="495"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
@@ -15620,10 +15620,10 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="L6" s="492" t="s">
+      <c r="L6" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="M6" s="492"/>
+      <c r="M6" s="493"/>
     </row>
     <row r="7" spans="1:13" ht="15.95" customHeight="1">
       <c r="A7" s="9" t="s">
@@ -15642,8 +15642,8 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
-      <c r="L7" s="493"/>
-      <c r="M7" s="493"/>
+      <c r="L7" s="494"/>
+      <c r="M7" s="494"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="358" t="s">
@@ -16722,10 +16722,10 @@
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
-      <c r="E54" s="490" t="s">
+      <c r="E54" s="491" t="s">
         <v>472</v>
       </c>
-      <c r="F54" s="490"/>
+      <c r="F54" s="491"/>
       <c r="G54" s="375">
         <v>143</v>
       </c>
@@ -16745,8 +16745,8 @@
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
-      <c r="E55" s="491"/>
-      <c r="F55" s="491"/>
+      <c r="E55" s="492"/>
+      <c r="F55" s="492"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
@@ -17135,7 +17135,7 @@
     <row r="77" spans="1:10">
       <c r="A77" s="86">
         <f ca="1">TODAY()</f>
-        <v>45859</v>
+        <v>45867</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -18201,10 +18201,10 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="492" t="s">
+      <c r="L7" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="M7" s="492"/>
+      <c r="M7" s="493"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="358" t="s">
@@ -18226,8 +18226,8 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="8"/>
-      <c r="L8" s="493"/>
-      <c r="M8" s="493"/>
+      <c r="L8" s="494"/>
+      <c r="M8" s="494"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="14"/>
@@ -19260,10 +19260,10 @@
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
-      <c r="E51" s="490" t="s">
+      <c r="E51" s="491" t="s">
         <v>472</v>
       </c>
-      <c r="F51" s="490"/>
+      <c r="F51" s="491"/>
       <c r="G51" s="375">
         <v>143</v>
       </c>
@@ -19283,8 +19283,8 @@
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
-      <c r="E52" s="491"/>
-      <c r="F52" s="491"/>
+      <c r="E52" s="492"/>
+      <c r="F52" s="492"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -19578,11 +19578,11 @@
       </c>
     </row>
     <row r="70" spans="1:11" ht="48" customHeight="1">
-      <c r="A70" s="495" t="s">
+      <c r="A70" s="496" t="s">
         <v>311</v>
       </c>
-      <c r="B70" s="495"/>
-      <c r="C70" s="495"/>
+      <c r="B70" s="496"/>
+      <c r="C70" s="496"/>
       <c r="D70" s="240"/>
       <c r="E70" s="241"/>
       <c r="F70" s="241"/>
@@ -19603,11 +19603,11 @@
       <c r="F71" s="246" t="s">
         <v>27</v>
       </c>
-      <c r="G71" s="496" t="s">
+      <c r="G71" s="497" t="s">
         <v>77</v>
       </c>
-      <c r="H71" s="496"/>
-      <c r="I71" s="496"/>
+      <c r="H71" s="497"/>
+      <c r="I71" s="497"/>
     </row>
     <row r="72" spans="1:11" ht="35.1" customHeight="1">
       <c r="A72" s="235" t="s">
@@ -19629,11 +19629,11 @@
       <c r="F72" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="G72" s="498" t="s">
+      <c r="G72" s="499" t="s">
         <v>306</v>
       </c>
-      <c r="H72" s="498"/>
-      <c r="I72" s="498"/>
+      <c r="H72" s="499"/>
+      <c r="I72" s="499"/>
     </row>
     <row r="73" spans="1:11" ht="45" customHeight="1">
       <c r="A73" s="235" t="s">
@@ -19654,11 +19654,11 @@
       <c r="F73" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="G73" s="498" t="s">
+      <c r="G73" s="499" t="s">
         <v>308</v>
       </c>
-      <c r="H73" s="498"/>
-      <c r="I73" s="498"/>
+      <c r="H73" s="499"/>
+      <c r="I73" s="499"/>
     </row>
     <row r="74" spans="1:11" ht="74.099999999999994" customHeight="1">
       <c r="A74" s="247" t="s">
@@ -19677,11 +19677,11 @@
       <c r="F74" s="250" t="s">
         <v>305</v>
       </c>
-      <c r="G74" s="497" t="s">
+      <c r="G74" s="498" t="s">
         <v>310</v>
       </c>
-      <c r="H74" s="497"/>
-      <c r="I74" s="497"/>
+      <c r="H74" s="498"/>
+      <c r="I74" s="498"/>
     </row>
     <row r="75" spans="1:11">
       <c r="E75" s="169">
@@ -19858,7 +19858,7 @@
     <row r="101" spans="1:11">
       <c r="A101" s="86">
         <f ca="1">TODAY()</f>
-        <v>45859</v>
+        <v>45867</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -19987,10 +19987,10 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="8"/>
-      <c r="L6" s="492" t="s">
+      <c r="L6" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="M6" s="492"/>
+      <c r="M6" s="493"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="9" t="s">
@@ -20010,8 +20010,8 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="493"/>
-      <c r="M7" s="493"/>
+      <c r="L7" s="494"/>
+      <c r="M7" s="494"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="358" t="s">
@@ -21048,10 +21048,10 @@
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
-      <c r="E51" s="490" t="s">
+      <c r="E51" s="491" t="s">
         <v>472</v>
       </c>
-      <c r="F51" s="490"/>
+      <c r="F51" s="491"/>
       <c r="G51" s="375">
         <v>143</v>
       </c>
@@ -21071,8 +21071,8 @@
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
-      <c r="E52" s="491"/>
-      <c r="F52" s="491"/>
+      <c r="E52" s="492"/>
+      <c r="F52" s="492"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -21468,7 +21468,7 @@
     <row r="73" spans="1:11">
       <c r="A73" s="86">
         <f ca="1">TODAY()</f>
-        <v>45859</v>
+        <v>45867</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -21556,9 +21556,10 @@
     <hyperlink ref="A75" r:id="rId6" display="https://www.extension.iastate.edu/legal" xr:uid="{AB2B17CD-D279-5740-8C20-3E2B07C4FD32}"/>
     <hyperlink ref="A83" r:id="rId7" xr:uid="{5A4D60D5-1D44-E34F-9615-E7E424081014}"/>
     <hyperlink ref="L6:M7" location="'Instructions &amp; summary data'!A1" display="Return to instructions page" xr:uid="{8413DB6A-378B-F546-8F7D-9040B541A9FE}"/>
+    <hyperlink ref="A80" r:id="rId8" xr:uid="{83813627-3D86-4FC8-B10E-4900D01E3003}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId8"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -21656,10 +21657,10 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="8"/>
-      <c r="L6" s="492" t="s">
+      <c r="L6" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="M6" s="492"/>
+      <c r="M6" s="493"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="9" t="s">
@@ -21679,8 +21680,8 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="493"/>
-      <c r="M7" s="493"/>
+      <c r="L7" s="494"/>
+      <c r="M7" s="494"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="358" t="s">
@@ -22668,10 +22669,10 @@
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
-      <c r="E49" s="490" t="s">
+      <c r="E49" s="491" t="s">
         <v>472</v>
       </c>
-      <c r="F49" s="490"/>
+      <c r="F49" s="491"/>
       <c r="G49" s="375">
         <v>143</v>
       </c>
@@ -22691,8 +22692,8 @@
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
-      <c r="E50" s="491"/>
-      <c r="F50" s="491"/>
+      <c r="E50" s="492"/>
+      <c r="F50" s="492"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -22981,11 +22982,11 @@
       <c r="K63" s="8"/>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" s="499" t="s">
+      <c r="A65" s="500" t="s">
         <v>311</v>
       </c>
-      <c r="B65" s="499"/>
-      <c r="C65" s="499"/>
+      <c r="B65" s="500"/>
+      <c r="C65" s="500"/>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="244"/>
@@ -23002,11 +23003,11 @@
       <c r="F66" s="246" t="s">
         <v>27</v>
       </c>
-      <c r="G66" s="496" t="s">
+      <c r="G66" s="497" t="s">
         <v>77</v>
       </c>
-      <c r="H66" s="496"/>
-      <c r="I66" s="496"/>
+      <c r="H66" s="497"/>
+      <c r="I66" s="497"/>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="235" t="s">
@@ -23028,11 +23029,11 @@
       <c r="F67" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="G67" s="498" t="s">
+      <c r="G67" s="499" t="s">
         <v>306</v>
       </c>
-      <c r="H67" s="498"/>
-      <c r="I67" s="498"/>
+      <c r="H67" s="499"/>
+      <c r="I67" s="499"/>
     </row>
     <row r="68" spans="1:11" ht="41.1" customHeight="1">
       <c r="A68" s="235" t="s">
@@ -23053,11 +23054,11 @@
       <c r="F68" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="G68" s="498" t="s">
+      <c r="G68" s="499" t="s">
         <v>308</v>
       </c>
-      <c r="H68" s="498"/>
-      <c r="I68" s="498"/>
+      <c r="H68" s="499"/>
+      <c r="I68" s="499"/>
     </row>
     <row r="69" spans="1:11" ht="81" customHeight="1">
       <c r="A69" s="247" t="s">
@@ -23076,11 +23077,11 @@
       <c r="F69" s="250" t="s">
         <v>305</v>
       </c>
-      <c r="G69" s="497" t="s">
+      <c r="G69" s="498" t="s">
         <v>310</v>
       </c>
-      <c r="H69" s="497"/>
-      <c r="I69" s="497"/>
+      <c r="H69" s="498"/>
+      <c r="I69" s="498"/>
     </row>
     <row r="70" spans="1:11">
       <c r="E70" s="169">
@@ -23242,7 +23243,7 @@
     <row r="88" spans="1:11">
       <c r="A88" s="86">
         <f ca="1">TODAY()</f>
-        <v>45859</v>
+        <v>45867</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -23403,10 +23404,10 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="492" t="s">
+      <c r="K5" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="L5" s="492"/>
+      <c r="L5" s="493"/>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="8"/>
@@ -23419,8 +23420,8 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="493"/>
-      <c r="L6" s="493"/>
+      <c r="K6" s="494"/>
+      <c r="L6" s="494"/>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="9" t="s">
@@ -26219,7 +26220,7 @@
     <row r="133" spans="1:11">
       <c r="A133" s="86">
         <f ca="1">TODAY()</f>
-        <v>45859</v>
+        <v>45867</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -26372,10 +26373,10 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="8"/>
-      <c r="L6" s="492" t="s">
+      <c r="L6" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="M6" s="492"/>
+      <c r="M6" s="493"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="9" t="s">
@@ -26393,8 +26394,8 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="493"/>
-      <c r="M7" s="493"/>
+      <c r="L7" s="494"/>
+      <c r="M7" s="494"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="358" t="s">
@@ -29177,7 +29178,7 @@
     <row r="133" spans="1:11">
       <c r="A133" s="86">
         <f ca="1">TODAY()</f>
-        <v>45859</v>
+        <v>45867</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -29635,10 +29636,10 @@
         <v>385</v>
       </c>
       <c r="F2" s="236"/>
-      <c r="N2" s="492" t="s">
+      <c r="N2" s="493" t="s">
         <v>549</v>
       </c>
-      <c r="O2" s="492"/>
+      <c r="O2" s="493"/>
     </row>
     <row r="3" spans="1:18" ht="42" customHeight="1" thickBot="1">
       <c r="A3" s="251" t="s">
@@ -29656,27 +29657,27 @@
       <c r="K3" s="88"/>
       <c r="L3" s="88"/>
       <c r="M3" s="88"/>
-      <c r="N3" s="493"/>
-      <c r="O3" s="493"/>
+      <c r="N3" s="494"/>
+      <c r="O3" s="494"/>
       <c r="P3" s="88"/>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>324</v>
       </c>
-      <c r="F4" s="500" t="s">
+      <c r="F4" s="501" t="s">
         <v>325</v>
       </c>
-      <c r="G4" s="500"/>
-      <c r="H4" s="500"/>
-      <c r="I4" s="500"/>
-      <c r="J4" s="500"/>
-      <c r="K4" s="500"/>
-      <c r="L4" s="500"/>
-      <c r="M4" s="500"/>
-      <c r="N4" s="500"/>
-      <c r="O4" s="500"/>
-      <c r="P4" s="500"/>
+      <c r="G4" s="501"/>
+      <c r="H4" s="501"/>
+      <c r="I4" s="501"/>
+      <c r="J4" s="501"/>
+      <c r="K4" s="501"/>
+      <c r="L4" s="501"/>
+      <c r="M4" s="501"/>
+      <c r="N4" s="501"/>
+      <c r="O4" s="501"/>
+      <c r="P4" s="501"/>
     </row>
     <row r="5" spans="1:18" ht="32.25" thickBot="1">
       <c r="A5" s="253"/>

--- a/PEWI Budgets 2024$ - 2025$ (021425).xlsx
+++ b/PEWI Budgets 2024$ - 2025$ (021425).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_pewi\PEWI-People-in-Ecosystem-and-Watershed-Integration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F4A016-C6CD-4F63-BFCC-FC07113D4CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4F05C2-AAF9-41C8-8CD8-DA610AEC53C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="4" xr2:uid="{2A59C1DF-064D-264D-B5F5-440AD859B569}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18240" firstSheet="4" activeTab="6" xr2:uid="{2A59C1DF-064D-264D-B5F5-440AD859B569}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions &amp; summary data" sheetId="19" r:id="rId1"/>
@@ -4446,41 +4446,41 @@
     <xf numFmtId="44" fontId="0" fillId="12" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="8" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -8518,16 +8518,16 @@
       <c r="L3" s="494"/>
     </row>
     <row r="4" spans="2:12" ht="33.75">
-      <c r="B4" s="508" t="s">
+      <c r="B4" s="505" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="509"/>
-      <c r="D4" s="509"/>
-      <c r="E4" s="509"/>
-      <c r="F4" s="509"/>
-      <c r="G4" s="509"/>
-      <c r="H4" s="509"/>
-      <c r="I4" s="510"/>
+      <c r="C4" s="506"/>
+      <c r="D4" s="506"/>
+      <c r="E4" s="506"/>
+      <c r="F4" s="506"/>
+      <c r="G4" s="506"/>
+      <c r="H4" s="506"/>
+      <c r="I4" s="507"/>
     </row>
     <row r="5" spans="2:12" ht="16.5" thickBot="1">
       <c r="B5" s="145" t="s">
@@ -8548,10 +8548,10 @@
       <c r="G5" s="146" t="s">
         <v>200</v>
       </c>
-      <c r="H5" s="511" t="s">
+      <c r="H5" s="508" t="s">
         <v>201</v>
       </c>
-      <c r="I5" s="512"/>
+      <c r="I5" s="509"/>
     </row>
     <row r="6" spans="2:12" ht="16.5" thickBot="1">
       <c r="B6" s="147"/>
@@ -8629,10 +8629,10 @@
       <c r="G9" s="150" t="s">
         <v>200</v>
       </c>
-      <c r="H9" s="513" t="s">
+      <c r="H9" s="510" t="s">
         <v>212</v>
       </c>
-      <c r="I9" s="514"/>
+      <c r="I9" s="511"/>
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="151" t="s">
@@ -8656,11 +8656,11 @@
         <f>F10/C6</f>
         <v>160</v>
       </c>
-      <c r="H10" s="505">
+      <c r="H10" s="512">
         <f>G10/$I$7</f>
         <v>290.90909090909088</v>
       </c>
-      <c r="I10" s="506"/>
+      <c r="I10" s="513"/>
     </row>
     <row r="11" spans="2:12" ht="17.25">
       <c r="B11" s="157" t="s">
@@ -8684,11 +8684,11 @@
         <f>F11/20</f>
         <v>0</v>
       </c>
-      <c r="H11" s="515">
+      <c r="H11" s="514">
         <f>G11/$I$7</f>
         <v>0</v>
       </c>
-      <c r="I11" s="516"/>
+      <c r="I11" s="515"/>
     </row>
     <row r="12" spans="2:12" ht="17.25">
       <c r="B12" s="151" t="s">
@@ -9137,11 +9137,11 @@
         <f>G26+G6+G30</f>
         <v>3496.809836065574</v>
       </c>
-      <c r="H31" s="505">
+      <c r="H31" s="512">
         <f t="shared" si="0"/>
         <v>5.2981967213114753</v>
       </c>
-      <c r="I31" s="506"/>
+      <c r="I31" s="513"/>
       <c r="J31" t="s">
         <v>242</v>
       </c>
@@ -9183,11 +9183,11 @@
       <c r="I33" s="168"/>
     </row>
     <row r="34" spans="1:12" ht="17.25">
-      <c r="B34" s="507" t="s">
+      <c r="B34" s="516" t="s">
         <v>245</v>
       </c>
-      <c r="C34" s="507"/>
-      <c r="D34" s="507"/>
+      <c r="C34" s="516"/>
+      <c r="D34" s="516"/>
       <c r="L34">
         <f>50/H38</f>
         <v>2.1917808219178081</v>
@@ -9224,13 +9224,11 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="K2:L3"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="H27:I27"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="H17:I17"/>
@@ -9243,11 +9241,13 @@
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="H25:I25"/>
     <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="K2:L3"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L8" r:id="rId1" xr:uid="{F7409163-740C-D24A-84CB-4E3439D40069}"/>
@@ -9283,16 +9283,16 @@
       <c r="L3" s="494"/>
     </row>
     <row r="4" spans="2:12" ht="33.75">
-      <c r="B4" s="508" t="s">
+      <c r="B4" s="505" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="509"/>
-      <c r="D4" s="509"/>
-      <c r="E4" s="509"/>
-      <c r="F4" s="509"/>
-      <c r="G4" s="509"/>
-      <c r="H4" s="509"/>
-      <c r="I4" s="510"/>
+      <c r="C4" s="506"/>
+      <c r="D4" s="506"/>
+      <c r="E4" s="506"/>
+      <c r="F4" s="506"/>
+      <c r="G4" s="506"/>
+      <c r="H4" s="506"/>
+      <c r="I4" s="507"/>
     </row>
     <row r="5" spans="2:12" ht="16.5" thickBot="1">
       <c r="B5" s="145" t="s">
@@ -9313,10 +9313,10 @@
       <c r="G5" s="146" t="s">
         <v>200</v>
       </c>
-      <c r="H5" s="511" t="s">
+      <c r="H5" s="508" t="s">
         <v>201</v>
       </c>
-      <c r="I5" s="512"/>
+      <c r="I5" s="509"/>
     </row>
     <row r="6" spans="2:12" ht="16.5" thickBot="1">
       <c r="B6" s="147"/>
@@ -9394,10 +9394,10 @@
       <c r="G9" s="150" t="s">
         <v>200</v>
       </c>
-      <c r="H9" s="513" t="s">
+      <c r="H9" s="510" t="s">
         <v>212</v>
       </c>
-      <c r="I9" s="514"/>
+      <c r="I9" s="511"/>
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="151" t="s">
@@ -9421,11 +9421,11 @@
         <f>F10/C6</f>
         <v>160</v>
       </c>
-      <c r="H10" s="505" t="e">
+      <c r="H10" s="512" t="e">
         <f>G10/$J$7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I10" s="506"/>
+      <c r="I10" s="513"/>
     </row>
     <row r="11" spans="2:12" ht="17.25">
       <c r="B11" s="157" t="s">
@@ -9449,11 +9449,11 @@
         <f>F11/20</f>
         <v>0</v>
       </c>
-      <c r="H11" s="515" t="e">
+      <c r="H11" s="514" t="e">
         <f t="shared" ref="H11" si="0">G11/$J$7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I11" s="516"/>
+      <c r="I11" s="515"/>
     </row>
     <row r="12" spans="2:12" ht="17.25">
       <c r="B12" s="151" t="s">
@@ -9928,11 +9928,11 @@
         <f>G27+G6+G31</f>
         <v>3556.809836065574</v>
       </c>
-      <c r="H32" s="505">
+      <c r="H32" s="512">
         <f t="shared" si="1"/>
         <v>5.3891058122205671</v>
       </c>
-      <c r="I32" s="506"/>
+      <c r="I32" s="513"/>
       <c r="J32" t="s">
         <v>242</v>
       </c>
@@ -9974,11 +9974,11 @@
       <c r="I34" s="168"/>
     </row>
     <row r="35" spans="1:9" ht="17.25">
-      <c r="B35" s="507" t="s">
+      <c r="B35" s="516" t="s">
         <v>245</v>
       </c>
-      <c r="C35" s="507"/>
-      <c r="D35" s="507"/>
+      <c r="C35" s="516"/>
+      <c r="D35" s="516"/>
     </row>
     <row r="36" spans="1:9" ht="17.25">
       <c r="B36" s="174" t="s">
@@ -9999,6 +9999,16 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
     <mergeCell ref="K2:L3"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="H28:I28"/>
@@ -10014,16 +10024,6 @@
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L8" r:id="rId1" xr:uid="{C10CBC37-B907-284D-A5CD-D379AFEFC3CE}"/>
@@ -17135,7 +17135,7 @@
     <row r="77" spans="1:10">
       <c r="A77" s="86">
         <f ca="1">TODAY()</f>
-        <v>45867</v>
+        <v>45873</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -19858,7 +19858,7 @@
     <row r="101" spans="1:11">
       <c r="A101" s="86">
         <f ca="1">TODAY()</f>
-        <v>45867</v>
+        <v>45873</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -21468,7 +21468,7 @@
     <row r="73" spans="1:11">
       <c r="A73" s="86">
         <f ca="1">TODAY()</f>
-        <v>45867</v>
+        <v>45873</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -23243,7 +23243,7 @@
     <row r="88" spans="1:11">
       <c r="A88" s="86">
         <f ca="1">TODAY()</f>
-        <v>45867</v>
+        <v>45873</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -23323,12 +23323,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086A57DC-7D68-DE46-98A4-FDAEE91B33A9}">
-  <dimension ref="A1:L138"/>
+  <dimension ref="A1:N139"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="2" max="2" width="17.125" customWidth="1"/>
     <col min="4" max="4" width="15.875" customWidth="1"/>
     <col min="5" max="5" width="16.625" customWidth="1"/>
+    <col min="14" max="14" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" thickBot="1">
@@ -23447,7 +23448,7 @@
       <c r="B8" s="359"/>
       <c r="C8" s="352"/>
       <c r="D8" s="91">
-        <v>1000</v>
+        <v>5899</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -23536,7 +23537,7 @@
       </c>
       <c r="J12" s="22" t="str">
         <f>D8&amp;" Acres"&amp;""</f>
-        <v>1000 Acres</v>
+        <v>5899 Acres</v>
       </c>
       <c r="K12" s="8"/>
     </row>
@@ -23561,7 +23562,7 @@
       </c>
       <c r="J13" s="24">
         <f t="shared" ref="J13:J20" si="1">$D$8*I13</f>
-        <v>6500</v>
+        <v>38343.5</v>
       </c>
       <c r="K13" s="8"/>
     </row>
@@ -23586,7 +23587,7 @@
       </c>
       <c r="J14" s="24">
         <f t="shared" si="1"/>
-        <v>25200</v>
+        <v>148654.79999999999</v>
       </c>
       <c r="K14" s="8"/>
     </row>
@@ -23611,7 +23612,7 @@
       </c>
       <c r="J15" s="24">
         <f t="shared" si="1"/>
-        <v>5500</v>
+        <v>32444.5</v>
       </c>
       <c r="K15" s="8"/>
     </row>
@@ -23636,7 +23637,7 @@
       </c>
       <c r="J16" s="24">
         <f t="shared" si="1"/>
-        <v>5500</v>
+        <v>32444.5</v>
       </c>
       <c r="K16" s="8"/>
     </row>
@@ -23661,7 +23662,7 @@
       </c>
       <c r="J17" s="24">
         <f t="shared" si="1"/>
-        <v>13200</v>
+        <v>77866.8</v>
       </c>
       <c r="K17" s="8"/>
     </row>
@@ -23738,7 +23739,7 @@
       </c>
       <c r="J20" s="30">
         <f t="shared" si="1"/>
-        <v>55900.000000000007</v>
+        <v>329754.10000000003</v>
       </c>
       <c r="K20" s="8"/>
     </row>
@@ -23753,15 +23754,15 @@
       <c r="F21" s="3"/>
       <c r="G21" s="24">
         <f>$D$8*G20</f>
-        <v>35300</v>
+        <v>208234.69999999998</v>
       </c>
       <c r="H21" s="24">
         <f>$D$8*H20</f>
-        <v>20600</v>
+        <v>121519.40000000001</v>
       </c>
       <c r="I21" s="30">
         <f>$D$8*I20</f>
-        <v>55900.000000000007</v>
+        <v>329754.10000000003</v>
       </c>
       <c r="J21" s="31"/>
       <c r="K21" s="8"/>
@@ -23822,7 +23823,7 @@
       </c>
       <c r="J24" s="22" t="str">
         <f>D8&amp;" Acres"&amp;""</f>
-        <v>1000 Acres</v>
+        <v>5899 Acres</v>
       </c>
       <c r="K24" s="8"/>
     </row>
@@ -23854,7 +23855,7 @@
       </c>
       <c r="J25" s="24">
         <f t="shared" ref="J25:J30" si="3">$D$8*I25</f>
-        <v>62699.999999999993</v>
+        <v>369867.3</v>
       </c>
       <c r="K25" s="8"/>
     </row>
@@ -23929,7 +23930,7 @@
       </c>
       <c r="J28" s="24">
         <f t="shared" si="3"/>
-        <v>22000</v>
+        <v>129778</v>
       </c>
       <c r="K28" s="8"/>
     </row>
@@ -23952,7 +23953,7 @@
       </c>
       <c r="J29" s="24">
         <f t="shared" si="3"/>
-        <v>26300</v>
+        <v>155143.70000000001</v>
       </c>
       <c r="K29" s="8"/>
     </row>
@@ -23999,7 +24000,7 @@
       </c>
       <c r="J31" s="30">
         <f>SUM(J25:J30)</f>
-        <v>111000</v>
+        <v>654789</v>
       </c>
       <c r="K31" s="8"/>
     </row>
@@ -24063,7 +24064,7 @@
       </c>
       <c r="J34" s="24">
         <f>$D$8*I34</f>
-        <v>20150</v>
+        <v>118864.84999999999</v>
       </c>
       <c r="K34" s="8"/>
     </row>
@@ -24117,7 +24118,7 @@
       </c>
       <c r="J36" s="30">
         <f>J34+J35</f>
-        <v>20150</v>
+        <v>118864.84999999999</v>
       </c>
       <c r="K36" s="8"/>
     </row>
@@ -24241,7 +24242,7 @@
       </c>
       <c r="J42" s="22" t="str">
         <f>D8&amp;" Acres"&amp;""</f>
-        <v>1000 Acres</v>
+        <v>5899 Acres</v>
       </c>
       <c r="K42" s="8"/>
     </row>
@@ -24303,7 +24304,7 @@
       </c>
       <c r="J44" s="24">
         <f>$D$8*I44</f>
-        <v>20299.999999999996</v>
+        <v>119749.69999999998</v>
       </c>
       <c r="K44" s="8"/>
     </row>
@@ -24335,7 +24336,7 @@
       </c>
       <c r="J45" s="24">
         <f>$D$8*I45</f>
-        <v>45000</v>
+        <v>265455</v>
       </c>
       <c r="K45" s="8"/>
     </row>
@@ -24401,7 +24402,7 @@
       </c>
       <c r="J48" s="30">
         <f>SUM(J43:J47)</f>
-        <v>65300</v>
+        <v>385204.69999999995</v>
       </c>
       <c r="K48" s="8"/>
     </row>
@@ -24473,7 +24474,7 @@
       </c>
       <c r="J51" s="24">
         <f>$D$8*I51</f>
-        <v>60449.999999999993</v>
+        <v>356594.55</v>
       </c>
       <c r="K51" s="8"/>
     </row>
@@ -24527,7 +24528,7 @@
       </c>
       <c r="J53" s="30">
         <f>J51+J52</f>
-        <v>60449.999999999993</v>
+        <v>356594.55</v>
       </c>
       <c r="K53" s="8"/>
     </row>
@@ -24588,7 +24589,7 @@
       </c>
       <c r="J56" s="30">
         <f>$D$8*I56</f>
-        <v>164000</v>
+        <v>967436</v>
       </c>
       <c r="K56" s="8"/>
     </row>
@@ -24651,7 +24652,7 @@
       </c>
       <c r="J59" s="24">
         <f>$D$8*I59</f>
-        <v>15100</v>
+        <v>89074.9</v>
       </c>
       <c r="K59" s="8"/>
     </row>
@@ -24676,7 +24677,7 @@
       </c>
       <c r="J60" s="24">
         <f>$D$8*I60</f>
-        <v>8100</v>
+        <v>47781.9</v>
       </c>
       <c r="K60" s="8"/>
     </row>
@@ -24701,7 +24702,7 @@
       </c>
       <c r="J61" s="24">
         <f>$D$8*I61</f>
-        <v>21000</v>
+        <v>123879</v>
       </c>
       <c r="K61" s="8"/>
     </row>
@@ -24736,7 +24737,7 @@
       </c>
       <c r="J62" s="24">
         <f>$D$8*I62</f>
-        <v>17924.999999999996</v>
+        <v>105739.57499999998</v>
       </c>
       <c r="K62" s="8"/>
     </row>
@@ -24824,16 +24825,16 @@
       <c r="F66" s="3"/>
       <c r="G66" s="23">
         <f>$D$8*G65</f>
-        <v>67375</v>
+        <v>397445.125</v>
       </c>
       <c r="H66" s="23">
         <f>$D$8*H65</f>
-        <v>38949.999999999993</v>
+        <v>229766.05</v>
       </c>
       <c r="I66" s="30"/>
       <c r="J66" s="30">
         <f>SUM(J58:J63)</f>
-        <v>62125</v>
+        <v>366475.375</v>
       </c>
       <c r="K66" s="8"/>
     </row>
@@ -24889,7 +24890,7 @@
       </c>
       <c r="J69" s="22" t="str">
         <f>D8&amp;" Acres"&amp;""</f>
-        <v>1000 Acres</v>
+        <v>5899 Acres</v>
       </c>
       <c r="K69" s="8"/>
     </row>
@@ -24916,7 +24917,7 @@
       </c>
       <c r="J70" s="23">
         <f>I70*D8</f>
-        <v>458424.99999999994</v>
+        <v>2704249.0749999997</v>
       </c>
       <c r="K70" s="8"/>
     </row>
@@ -24997,7 +24998,7 @@
       </c>
       <c r="J74" s="123">
         <f>I74*D$8</f>
-        <v>632500</v>
+        <v>3731117.5</v>
       </c>
       <c r="K74" s="8"/>
     </row>
@@ -25018,7 +25019,7 @@
       </c>
       <c r="J75" s="76">
         <f>J74</f>
-        <v>632500</v>
+        <v>3731117.5</v>
       </c>
       <c r="K75" s="8"/>
     </row>
@@ -25042,7 +25043,7 @@
       </c>
       <c r="J76" s="56">
         <f>J70-J75</f>
-        <v>-174075.00000000006</v>
+        <v>-1026868.4250000003</v>
       </c>
       <c r="K76" s="8"/>
     </row>
@@ -25213,7 +25214,7 @@
       </c>
       <c r="J85" s="22" t="str">
         <f>D8&amp;" Acres"&amp;""</f>
-        <v>1000 Acres</v>
+        <v>5899 Acres</v>
       </c>
       <c r="K85" s="8"/>
     </row>
@@ -25238,7 +25239,7 @@
       </c>
       <c r="J86" s="24">
         <f>$D$8*I86</f>
-        <v>4000</v>
+        <v>23596</v>
       </c>
       <c r="K86" s="8"/>
     </row>
@@ -25287,7 +25288,7 @@
       </c>
       <c r="J88" s="24">
         <f>$D$8*I88</f>
-        <v>32421.999999999996</v>
+        <v>191257.378</v>
       </c>
       <c r="K88" s="8"/>
     </row>
@@ -25319,7 +25320,7 @@
       </c>
       <c r="J89" s="24">
         <f>$D$8*I89</f>
-        <v>77399.999999999985</v>
+        <v>456582.6</v>
       </c>
       <c r="K89" s="8"/>
     </row>
@@ -25342,7 +25343,7 @@
       </c>
       <c r="J90" s="24">
         <f>$D$8*I90</f>
-        <v>4650</v>
+        <v>27430.350000000002</v>
       </c>
       <c r="K90" s="8"/>
     </row>
@@ -25392,7 +25393,7 @@
       </c>
       <c r="J92" s="30">
         <f>SUM(J88:J91)</f>
-        <v>114471.99999999999</v>
+        <v>675270.32799999998</v>
       </c>
       <c r="K92" s="8"/>
     </row>
@@ -25447,7 +25448,7 @@
       </c>
       <c r="J95" s="24">
         <f>$D$8*I95</f>
-        <v>15100</v>
+        <v>89074.9</v>
       </c>
       <c r="K95" s="8"/>
     </row>
@@ -25472,7 +25473,7 @@
       </c>
       <c r="J96" s="24">
         <f>$D$8*I96</f>
-        <v>8100</v>
+        <v>47781.9</v>
       </c>
       <c r="K96" s="8"/>
     </row>
@@ -25497,7 +25498,7 @@
       </c>
       <c r="J97" s="24">
         <f>$D$8*I97</f>
-        <v>21000</v>
+        <v>123879</v>
       </c>
       <c r="K97" s="8"/>
     </row>
@@ -25532,7 +25533,7 @@
       </c>
       <c r="J98" s="24">
         <f>$D$8*I98</f>
-        <v>30830.999999999996</v>
+        <v>181872.06899999999</v>
       </c>
       <c r="K98" s="8"/>
     </row>
@@ -25605,7 +25606,7 @@
       </c>
       <c r="J101" s="24">
         <f>I101*D8</f>
-        <v>207631</v>
+        <v>1224815.2690000001</v>
       </c>
       <c r="K101" s="8"/>
     </row>
@@ -25667,7 +25668,7 @@
       </c>
       <c r="J104" s="24">
         <f>$D$8*I104</f>
-        <v>107466.39799999999</v>
+        <v>633944.2818019999</v>
       </c>
       <c r="K104" s="8"/>
     </row>
@@ -25721,7 +25722,7 @@
       </c>
       <c r="J106" s="30">
         <f>J104+J105</f>
-        <v>107466.39799999999</v>
+        <v>633944.2818019999</v>
       </c>
       <c r="K106" s="8"/>
     </row>
@@ -25776,7 +25777,7 @@
       </c>
       <c r="J109" s="30">
         <f>$D$8*I109</f>
-        <v>100000</v>
+        <v>589900</v>
       </c>
       <c r="K109" s="8"/>
     </row>
@@ -25834,7 +25835,7 @@
       </c>
       <c r="J112" s="22" t="str">
         <f>D8&amp;" Acres"&amp;""</f>
-        <v>1000 Acres</v>
+        <v>5899 Acres</v>
       </c>
       <c r="K112" s="8"/>
     </row>
@@ -25861,7 +25862,7 @@
       </c>
       <c r="J113" s="29">
         <f>I113*D8</f>
-        <v>602919.39800000004</v>
+        <v>3556621.528802</v>
       </c>
       <c r="K113" s="8"/>
     </row>
@@ -25984,7 +25985,7 @@
       </c>
       <c r="J119" s="29">
         <f>I119*D8</f>
-        <v>554754.59866666666</v>
+        <v>3272497.3775346666</v>
       </c>
       <c r="K119" s="8"/>
     </row>
@@ -26051,7 +26052,7 @@
       </c>
       <c r="J122" s="123">
         <f>I122*D$8</f>
-        <v>1661366.6666666665</v>
+        <v>9800401.9666666668</v>
       </c>
       <c r="K122" s="8"/>
     </row>
@@ -26110,7 +26111,7 @@
       </c>
       <c r="J125" s="393">
         <f>J122-J119</f>
-        <v>1106612.068</v>
+        <v>6527904.5891319998</v>
       </c>
       <c r="K125" s="8"/>
     </row>
@@ -26157,7 +26158,7 @@
       <c r="J128" s="3"/>
       <c r="K128" s="8"/>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:14">
       <c r="A129" s="82" t="s">
         <v>78</v>
       </c>
@@ -26172,7 +26173,7 @@
       <c r="J129" s="3"/>
       <c r="K129" s="8"/>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:14">
       <c r="A130" s="8" t="s">
         <v>82</v>
       </c>
@@ -26186,8 +26187,12 @@
       <c r="I130" s="3"/>
       <c r="J130" s="3"/>
       <c r="K130" s="8"/>
-    </row>
-    <row r="131" spans="1:11">
+      <c r="N130" s="173">
+        <f>I119*5889</f>
+        <v>3266949.8315479998</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14">
       <c r="A131" s="84" t="s">
         <v>83</v>
       </c>
@@ -26202,7 +26207,7 @@
       <c r="J131" s="3"/>
       <c r="K131" s="8"/>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:14">
       <c r="A132" s="6" t="s">
         <v>84</v>
       </c>
@@ -26217,10 +26222,10 @@
       <c r="J132" s="3"/>
       <c r="K132" s="8"/>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:14">
       <c r="A133" s="86">
         <f ca="1">TODAY()</f>
-        <v>45867</v>
+        <v>45873</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -26233,7 +26238,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="8"/>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:14">
       <c r="A134" s="100"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -26246,14 +26251,24 @@
       <c r="J134" s="3"/>
       <c r="K134" s="8"/>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:14">
       <c r="A137" s="347" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:14">
       <c r="A138" s="378" t="s">
         <v>320</v>
+      </c>
+      <c r="N138" s="173">
+        <f>D122*4.3</f>
+        <v>1087.8999999999999</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14">
+      <c r="N139" s="173">
+        <f>N138*5889</f>
+        <v>6406643.0999999996</v>
       </c>
     </row>
   </sheetData>
@@ -29178,7 +29193,7 @@
     <row r="133" spans="1:11">
       <c r="A133" s="86">
         <f ca="1">TODAY()</f>
-        <v>45867</v>
+        <v>45873</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
